--- a/pcb/robot/gerbers/POS_JLCPCB.xlsx
+++ b/pcb/robot/gerbers/POS_JLCPCB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JHORDAN\FREELANCE\PROYECTOS\KICAD_USB_PD_MODULAR\Github\smartphone-robot-cad\pcb\robot\gerbers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68C60EC-CD50-4F15-9760-27250F3E526A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F882ECDE-7E0D-42B2-90BD-343C79F6A25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="290">
   <si>
     <t>Designator</t>
   </si>
@@ -237,18 +237,9 @@
     <t>C83</t>
   </si>
   <si>
-    <t>C84</t>
-  </si>
-  <si>
-    <t>C85</t>
-  </si>
-  <si>
     <t>C86</t>
   </si>
   <si>
-    <t>C87</t>
-  </si>
-  <si>
     <t>C88</t>
   </si>
   <si>
@@ -438,9 +429,6 @@
     <t>R8</t>
   </si>
   <si>
-    <t>R9</t>
-  </si>
-  <si>
     <t>R10</t>
   </si>
   <si>
@@ -531,15 +519,9 @@
     <t>R52</t>
   </si>
   <si>
-    <t>R53</t>
-  </si>
-  <si>
     <t>R54</t>
   </si>
   <si>
-    <t>R55</t>
-  </si>
-  <si>
     <t>R56</t>
   </si>
   <si>
@@ -633,9 +615,6 @@
     <t>R92</t>
   </si>
   <si>
-    <t>R93</t>
-  </si>
-  <si>
     <t>R94</t>
   </si>
   <si>
@@ -789,9 +768,6 @@
     <t>U13</t>
   </si>
   <si>
-    <t>U14</t>
-  </si>
-  <si>
     <t>U18</t>
   </si>
   <si>
@@ -909,7 +885,16 @@
     <t>bottom</t>
   </si>
   <si>
-    <t>C81</t>
+    <t>C45</t>
+  </si>
+  <si>
+    <t>C46</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>U11</t>
   </si>
 </sst>
 </file>
@@ -1287,16 +1272,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>251</v>
       </c>
       <c r="B2" s="2">
-        <v>46.1</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2">
-        <v>38.299999999999997</v>
+        <v>50.164999999999999</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E2" s="2">
         <v>0</v>
@@ -1304,50 +1289,50 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>252</v>
       </c>
       <c r="B3" s="2">
-        <v>9.8800000000000008</v>
+        <v>13.495207000000001</v>
       </c>
       <c r="C3" s="2">
-        <v>29.49</v>
+        <v>34.016168999999998</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E3" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>253</v>
       </c>
       <c r="B4" s="2">
-        <v>11.99</v>
+        <v>9.1</v>
       </c>
       <c r="C4" s="2">
-        <v>26.85</v>
+        <v>40.5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E4" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>254</v>
       </c>
       <c r="B5" s="2">
-        <v>63.016800000000003</v>
+        <v>10.595207</v>
       </c>
       <c r="C5" s="2">
-        <v>40.689700000000002</v>
+        <v>34.016168999999998</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E5" s="2">
         <v>180</v>
@@ -1355,67 +1340,67 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>255</v>
       </c>
       <c r="B6" s="2">
-        <v>6.3797930000000003</v>
+        <v>8.4</v>
       </c>
       <c r="C6" s="2">
-        <v>54.952869</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E6" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>256</v>
       </c>
       <c r="B7" s="2">
-        <v>11.6972</v>
+        <v>70.75</v>
       </c>
       <c r="C7" s="2">
-        <v>41.7301</v>
+        <v>59.25</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E7" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>257</v>
       </c>
       <c r="B8" s="2">
-        <v>13.6784</v>
+        <v>65.27</v>
       </c>
       <c r="C8" s="2">
-        <v>41.7301</v>
+        <v>59.25</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E8" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>258</v>
       </c>
       <c r="B9" s="2">
-        <v>12.713200000000001</v>
+        <v>18.2</v>
       </c>
       <c r="C9" s="2">
-        <v>41.7301</v>
+        <v>39.1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E9" s="2">
         <v>90</v>
@@ -1423,84 +1408,84 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>259</v>
       </c>
       <c r="B10" s="2">
-        <v>14.643599999999999</v>
+        <v>53.75</v>
       </c>
       <c r="C10" s="2">
-        <v>41.7301</v>
+        <v>67.38</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E10" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>260</v>
       </c>
       <c r="B11" s="2">
-        <v>17.968399999999999</v>
+        <v>57.55</v>
       </c>
       <c r="C11" s="2">
-        <v>38.834499999999998</v>
+        <v>67.38</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E11" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>261</v>
       </c>
       <c r="B12" s="2">
-        <v>20.195207</v>
+        <v>52.45</v>
       </c>
       <c r="C12" s="2">
-        <v>34.527130999999997</v>
+        <v>65.525000000000006</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E12" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>262</v>
       </c>
       <c r="B13" s="2">
-        <v>8.4700000000000006</v>
+        <v>54.7</v>
       </c>
       <c r="C13" s="2">
-        <v>41.3</v>
+        <v>67.38</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E13" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>263</v>
       </c>
       <c r="B14" s="2">
-        <v>15.6088</v>
+        <v>53.4</v>
       </c>
       <c r="C14" s="2">
-        <v>41.7301</v>
+        <v>65.525000000000006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E14" s="2">
         <v>90</v>
@@ -1508,118 +1493,118 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>18</v>
+        <v>264</v>
       </c>
       <c r="B15" s="2">
-        <v>63.063892000000003</v>
+        <v>47.55</v>
       </c>
       <c r="C15" s="2">
-        <v>49.296168999999999</v>
+        <v>65.55</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E15" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="B16" s="2">
-        <v>51.07</v>
+        <v>56.6</v>
       </c>
       <c r="C16" s="2">
-        <v>49.5</v>
+        <v>67.38</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E16" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="B17" s="2">
-        <v>47.9</v>
+        <v>46.6</v>
       </c>
       <c r="C17" s="2">
-        <v>52.9</v>
+        <v>65.55</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E17" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>21</v>
+        <v>267</v>
       </c>
       <c r="B18" s="2">
-        <v>44.65</v>
+        <v>55.65</v>
       </c>
       <c r="C18" s="2">
-        <v>53.9</v>
+        <v>67.38</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E18" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>22</v>
+        <v>268</v>
       </c>
       <c r="B19" s="2">
-        <v>38</v>
+        <v>51.5</v>
       </c>
       <c r="C19" s="2">
-        <v>37</v>
+        <v>65.55</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E19" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>23</v>
+        <v>269</v>
       </c>
       <c r="B20" s="2">
-        <v>42.05</v>
+        <v>45.65</v>
       </c>
       <c r="C20" s="2">
-        <v>36.9</v>
+        <v>65.55</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E20" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>24</v>
+        <v>270</v>
       </c>
       <c r="B21" s="2">
-        <v>40.844892000000002</v>
+        <v>55.45</v>
       </c>
       <c r="C21" s="2">
-        <v>35.156168999999998</v>
+        <v>59.5</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E21" s="2">
         <v>180</v>
@@ -1627,33 +1612,33 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>271</v>
       </c>
       <c r="B22" s="2">
-        <v>48.496892000000003</v>
+        <v>57.3</v>
       </c>
       <c r="C22" s="2">
-        <v>37.541168999999996</v>
+        <v>61.45</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E22" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>26</v>
+        <v>272</v>
       </c>
       <c r="B23" s="2">
-        <v>40.844892000000002</v>
+        <v>54.9</v>
       </c>
       <c r="C23" s="2">
-        <v>30.584168999999999</v>
+        <v>58.3</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E23" s="2">
         <v>180</v>
@@ -1661,33 +1646,33 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>27</v>
+        <v>273</v>
       </c>
       <c r="B24" s="2">
-        <v>49.75</v>
+        <v>54.35</v>
       </c>
       <c r="C24" s="2">
-        <v>37</v>
+        <v>65.525000000000006</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E24" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>28</v>
+        <v>274</v>
       </c>
       <c r="B25" s="2">
-        <v>49.861891999999997</v>
+        <v>33.5</v>
       </c>
       <c r="C25" s="2">
-        <v>34.267169000000003</v>
+        <v>27.824999999999999</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E25" s="2">
         <v>90</v>
@@ -1695,84 +1680,84 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>29</v>
+        <v>275</v>
       </c>
       <c r="B26" s="2">
-        <v>49.861891999999997</v>
+        <v>40</v>
       </c>
       <c r="C26" s="2">
-        <v>31.219169000000001</v>
+        <v>7.15</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E26" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>30</v>
+        <v>276</v>
       </c>
       <c r="B27" s="2">
-        <v>43.511892000000003</v>
+        <v>46.5</v>
       </c>
       <c r="C27" s="2">
-        <v>28.077131000000001</v>
+        <v>27.824999999999999</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E27" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>31</v>
+        <v>277</v>
       </c>
       <c r="B28" s="2">
-        <v>45.543892</v>
+        <v>39.9</v>
       </c>
       <c r="C28" s="2">
-        <v>28.077131000000001</v>
+        <v>15.6</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E28" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>32</v>
+        <v>278</v>
       </c>
       <c r="B29" s="2">
-        <v>47.25</v>
+        <v>21.8</v>
       </c>
       <c r="C29" s="2">
-        <v>28.077131000000001</v>
+        <v>39.1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E29" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>33</v>
+        <v>279</v>
       </c>
       <c r="B30" s="2">
-        <v>23.178201000000001</v>
+        <v>63.075000000000003</v>
       </c>
       <c r="C30" s="2">
-        <v>33.856099999999998</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E30" s="2">
         <v>0</v>
@@ -1780,220 +1765,220 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>280</v>
       </c>
       <c r="B31" s="2">
-        <v>18.5044</v>
+        <v>40</v>
       </c>
       <c r="C31" s="2">
-        <v>35.989699999999999</v>
+        <v>29.824999999999999</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E31" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>35</v>
+        <v>281</v>
       </c>
       <c r="B32" s="2">
-        <v>25.7</v>
+        <v>70.650000000000006</v>
       </c>
       <c r="C32" s="2">
-        <v>41.5</v>
+        <v>60.15</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E32" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>36</v>
+        <v>282</v>
       </c>
       <c r="B33" s="2">
-        <v>28.88</v>
+        <v>65.8</v>
       </c>
       <c r="C33" s="2">
-        <v>36.5</v>
+        <v>60.15</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E33" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2" t="s">
-        <v>37</v>
+        <v>283</v>
       </c>
       <c r="B34" s="2">
-        <v>50.2</v>
+        <v>70.8</v>
       </c>
       <c r="C34" s="2">
-        <v>15.18</v>
+        <v>61.95</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E34" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>38</v>
+        <v>284</v>
       </c>
       <c r="B35" s="2">
-        <v>38.799999999999997</v>
+        <v>66.3</v>
       </c>
       <c r="C35" s="2">
-        <v>15.6</v>
+        <v>61.95</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="E35" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="B36" s="2">
-        <v>49</v>
+        <v>46.1</v>
       </c>
       <c r="C36" s="2">
-        <v>15.475</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E36" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="B37" s="2">
-        <v>37.6</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="C37" s="2">
-        <v>14.975</v>
+        <v>29.49</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E37" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B38" s="2">
-        <v>13.717499999999999</v>
+        <v>11.99</v>
       </c>
       <c r="C38" s="2">
-        <v>21.42</v>
+        <v>26.85</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E38" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="B39" s="2">
-        <v>17.809999999999999</v>
+        <v>63.024999999999999</v>
       </c>
       <c r="C39" s="2">
-        <v>43.083799999999997</v>
+        <v>39.409999999999997</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E39" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="B40" s="2">
-        <v>19.2</v>
+        <v>6.3797930000000003</v>
       </c>
       <c r="C40" s="2">
-        <v>44</v>
+        <v>54.952869</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E40" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="B41" s="2">
-        <v>15.4948</v>
+        <v>11.6972</v>
       </c>
       <c r="C41" s="2">
-        <v>44.724400000000003</v>
+        <v>41.7301</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E41" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="B42" s="2">
-        <v>15.4948</v>
+        <v>13.6784</v>
       </c>
       <c r="C42" s="2">
-        <v>47.772399999999998</v>
+        <v>41.7301</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E42" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B43" s="2">
-        <v>17.3124</v>
+        <v>12.713200000000001</v>
       </c>
       <c r="C43" s="2">
-        <v>51.573300000000003</v>
+        <v>41.7301</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E43" s="2">
         <v>90</v>
@@ -2001,67 +1986,67 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="B44" s="2">
-        <v>19.598400000000002</v>
+        <v>14.643599999999999</v>
       </c>
       <c r="C44" s="2">
-        <v>50.811300000000003</v>
+        <v>41.7301</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E44" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="B45" s="2">
-        <v>21.859000000000002</v>
+        <v>17.968399999999999</v>
       </c>
       <c r="C45" s="2">
-        <v>51.573300000000003</v>
+        <v>38.834499999999998</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E45" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="B46" s="2">
-        <v>21.880400000000002</v>
+        <v>20.195207</v>
       </c>
       <c r="C46" s="2">
-        <v>54.599699999999999</v>
+        <v>34.527130999999997</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E46" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="B47" s="2">
-        <v>21.9</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="C47" s="2">
-        <v>56.48</v>
+        <v>41.3</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E47" s="2">
         <v>90</v>
@@ -2069,33 +2054,33 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="B48" s="2">
-        <v>24.6784</v>
+        <v>15.6088</v>
       </c>
       <c r="C48" s="2">
-        <v>42.554931000000003</v>
+        <v>41.7301</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E48" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="B49" s="2">
-        <v>26.202400000000001</v>
+        <v>63.063892000000003</v>
       </c>
       <c r="C49" s="2">
-        <v>45.527130999999997</v>
+        <v>49.296168999999999</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E49" s="2">
         <v>-90</v>
@@ -2103,50 +2088,50 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="B50" s="2">
-        <v>26.2</v>
+        <v>51.07</v>
       </c>
       <c r="C50" s="2">
-        <v>43.62</v>
+        <v>49.5</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E50" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="B51" s="2">
-        <v>38.174599999999998</v>
+        <v>47.9</v>
       </c>
       <c r="C51" s="2">
-        <v>50.7044</v>
+        <v>52.9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E51" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="B52" s="2">
-        <v>39.695207000000003</v>
+        <v>44.65</v>
       </c>
       <c r="C52" s="2">
-        <v>50.727131</v>
+        <v>53.9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E52" s="2">
         <v>90</v>
@@ -2154,152 +2139,152 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B53" s="2">
-        <v>35.954199000000003</v>
+        <v>38</v>
       </c>
       <c r="C53" s="2">
-        <v>40.634799999999998</v>
+        <v>37</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E53" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="B54" s="2">
-        <v>34.430199000000002</v>
+        <v>42.05</v>
       </c>
       <c r="C54" s="2">
-        <v>40.634799999999998</v>
+        <v>36.9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E54" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="B55" s="2">
-        <v>34.836599</v>
+        <v>40.844892000000002</v>
       </c>
       <c r="C55" s="2">
-        <v>50.693199999999997</v>
+        <v>35.156168999999998</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E55" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="B56" s="2">
-        <v>29.75</v>
+        <v>48.496892000000003</v>
       </c>
       <c r="C56" s="2">
-        <v>46.7</v>
+        <v>37.541168999999996</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E56" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="B57" s="2">
-        <v>37</v>
+        <v>40.844892000000002</v>
       </c>
       <c r="C57" s="2">
-        <v>42.1</v>
+        <v>30.584168999999999</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E57" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="B58" s="2">
-        <v>43.75</v>
+        <v>49.75</v>
       </c>
       <c r="C58" s="2">
-        <v>20.75</v>
+        <v>37</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E58" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="B59" s="2">
-        <v>30.85</v>
+        <v>49.861891999999997</v>
       </c>
       <c r="C59" s="2">
-        <v>44.087200000000003</v>
+        <v>34.267169000000003</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E59" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="B60" s="2">
-        <v>47.25</v>
+        <v>49.861891999999997</v>
       </c>
       <c r="C60" s="2">
-        <v>41</v>
+        <v>31.219169000000001</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E60" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="B61" s="2">
-        <v>39.995207000000001</v>
+        <v>43.511892000000003</v>
       </c>
       <c r="C61" s="2">
-        <v>46.427131000000003</v>
+        <v>28.077131000000001</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E61" s="2">
         <v>90</v>
@@ -2307,203 +2292,203 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="B62" s="2">
-        <v>45.769199999999998</v>
+        <v>45.543892</v>
       </c>
       <c r="C62" s="2">
-        <v>40.987200000000001</v>
+        <v>28.077131000000001</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E62" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="B63" s="2">
-        <v>28.9</v>
+        <v>47.25</v>
       </c>
       <c r="C63" s="2">
-        <v>43.9</v>
+        <v>28.077131000000001</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E63" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="B64" s="2">
-        <v>38.495207000000001</v>
+        <v>23.178201000000001</v>
       </c>
       <c r="C64" s="2">
-        <v>46.452131000000001</v>
+        <v>33.856099999999998</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E64" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2" t="s">
-        <v>294</v>
+        <v>34</v>
       </c>
       <c r="B65" s="2">
-        <v>49</v>
+        <v>18.5044</v>
       </c>
       <c r="C65" s="2">
-        <v>40.799999999999997</v>
+        <v>35.989699999999999</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E65" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="B66" s="2">
-        <v>51.2</v>
+        <v>25.7</v>
       </c>
       <c r="C66" s="2">
-        <v>40.25</v>
+        <v>41.5</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E66" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="B67" s="2">
-        <v>53.5</v>
+        <v>28.88</v>
       </c>
       <c r="C67" s="2">
-        <v>40.25</v>
+        <v>36.5</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E67" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="B68" s="2">
-        <v>72.099999999999994</v>
+        <v>50.2</v>
       </c>
       <c r="C68" s="2">
-        <v>39.85</v>
+        <v>15.18</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E68" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="B69" s="2">
-        <v>63.016800000000003</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="C69" s="2">
-        <v>37.689700000000002</v>
+        <v>15.6</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E69" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="B70" s="2">
-        <v>25.725000000000001</v>
+        <v>49</v>
       </c>
       <c r="C70" s="2">
-        <v>23</v>
+        <v>15.475</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E70" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="B71" s="2">
-        <v>63.016800000000003</v>
+        <v>37.6</v>
       </c>
       <c r="C71" s="2">
-        <v>39.189700000000002</v>
+        <v>14.975</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E71" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="B72" s="2">
-        <v>68.047799999999995</v>
+        <v>13.717499999999999</v>
       </c>
       <c r="C72" s="2">
-        <v>44.480699999999999</v>
+        <v>21.42</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E72" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2" t="s">
-        <v>75</v>
+        <v>286</v>
       </c>
       <c r="B73" s="2">
-        <v>53.225000000000001</v>
+        <v>63.03</v>
       </c>
       <c r="C73" s="2">
-        <v>20.725000000000001</v>
+        <v>37.85</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E73" s="2">
         <v>0</v>
@@ -2511,33 +2496,33 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2" t="s">
-        <v>76</v>
+        <v>287</v>
       </c>
       <c r="B74" s="2">
-        <v>35.299999999999997</v>
+        <v>73.47</v>
       </c>
       <c r="C74" s="2">
-        <v>23</v>
+        <v>41.15</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E74" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="B75" s="2">
-        <v>49.2</v>
+        <v>17.809999999999999</v>
       </c>
       <c r="C75" s="2">
-        <v>27.3</v>
+        <v>43.083799999999997</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E75" s="2">
         <v>-90</v>
@@ -2545,339 +2530,339 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="B76" s="2">
-        <v>72.55</v>
+        <v>19.2</v>
       </c>
       <c r="C76" s="2">
-        <v>44.38</v>
+        <v>44</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E76" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="B77" s="2">
-        <v>71.2</v>
+        <v>15.4948</v>
       </c>
       <c r="C77" s="2">
-        <v>44.5</v>
+        <v>44.724400000000003</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E77" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="B78" s="2">
-        <v>70.430000000000007</v>
+        <v>15.4948</v>
       </c>
       <c r="C78" s="2">
-        <v>40.75</v>
+        <v>47.772399999999998</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E78" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="B79" s="2">
-        <v>71.2</v>
+        <v>17.3124</v>
       </c>
       <c r="C79" s="2">
-        <v>38.4</v>
+        <v>51.573300000000003</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E79" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="B80" s="2">
-        <v>23.725000000000001</v>
+        <v>19.598400000000002</v>
       </c>
       <c r="C80" s="2">
-        <v>58.95</v>
+        <v>50.811300000000003</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E80" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B81" s="2">
-        <v>41</v>
+        <v>21.859000000000002</v>
       </c>
       <c r="C81" s="2">
-        <v>28.024999999999999</v>
+        <v>51.573300000000003</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E81" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="B82" s="2">
-        <v>60.711891999999999</v>
+        <v>21.880400000000002</v>
       </c>
       <c r="C82" s="2">
-        <v>41.491168999999999</v>
+        <v>54.599699999999999</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E82" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="B83" s="2">
-        <v>57.141891999999999</v>
+        <v>21.9</v>
       </c>
       <c r="C83" s="2">
-        <v>50.561169</v>
+        <v>56.48</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E83" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="B84" s="2">
-        <v>60.486891999999997</v>
+        <v>24.6784</v>
       </c>
       <c r="C84" s="2">
-        <v>45.566169000000002</v>
+        <v>42.554931000000003</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E84" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="B85" s="2">
-        <v>53.91</v>
+        <v>26.202400000000001</v>
       </c>
       <c r="C85" s="2">
-        <v>54.92</v>
+        <v>45.527130999999997</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E85" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="B86" s="2">
-        <v>30.675000000000001</v>
+        <v>26.2</v>
       </c>
       <c r="C86" s="2">
-        <v>53.65</v>
+        <v>43.62</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E86" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="B87" s="2">
-        <v>30.65</v>
+        <v>38.174599999999998</v>
       </c>
       <c r="C87" s="2">
-        <v>56</v>
+        <v>50.7044</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E87" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="B88" s="2">
-        <v>30.65</v>
+        <v>39.695207000000003</v>
       </c>
       <c r="C88" s="2">
-        <v>58.3</v>
+        <v>50.727131</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E88" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="B89" s="2">
-        <v>57.55</v>
+        <v>35.954199000000003</v>
       </c>
       <c r="C89" s="2">
-        <v>62.65</v>
+        <v>40.634799999999998</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E89" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="B90" s="2">
-        <v>56.75</v>
+        <v>34.430199000000002</v>
       </c>
       <c r="C90" s="2">
-        <v>65.900000000000006</v>
+        <v>40.634799999999998</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E90" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="B91" s="2">
-        <v>60</v>
+        <v>34.836599</v>
       </c>
       <c r="C91" s="2">
-        <v>61.8</v>
+        <v>50.693199999999997</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E91" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="B92" s="2">
-        <v>53.35</v>
+        <v>29.75</v>
       </c>
       <c r="C92" s="2">
-        <v>65.81</v>
+        <v>46.7</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E92" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="B93" s="2">
-        <v>56.274999999999999</v>
+        <v>37</v>
       </c>
       <c r="C93" s="2">
-        <v>59.2</v>
+        <v>42.1</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E93" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="B94" s="2">
-        <v>48.36</v>
+        <v>43.75</v>
       </c>
       <c r="C94" s="2">
-        <v>58.575000000000003</v>
+        <v>20.75</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E94" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="B95" s="2">
-        <v>46.9</v>
+        <v>30.85</v>
       </c>
       <c r="C95" s="2">
-        <v>58.575000000000003</v>
+        <v>44.087200000000003</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E95" s="2">
         <v>-90</v>
@@ -2885,16 +2870,16 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="B96" s="2">
-        <v>44.55</v>
+        <v>47.25</v>
       </c>
       <c r="C96" s="2">
-        <v>57.75</v>
+        <v>41</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E96" s="2">
         <v>-90</v>
@@ -2902,33 +2887,33 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="B97" s="2">
-        <v>50.6</v>
+        <v>39.995207000000001</v>
       </c>
       <c r="C97" s="2">
-        <v>61.58</v>
+        <v>46.427131000000003</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E97" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="B98" s="2">
-        <v>41.35</v>
+        <v>45.769199999999998</v>
       </c>
       <c r="C98" s="2">
-        <v>57.75</v>
+        <v>40.987200000000001</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E98" s="2">
         <v>-90</v>
@@ -2936,16 +2921,16 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="B99" s="2">
-        <v>49.1</v>
+        <v>28.9</v>
       </c>
       <c r="C99" s="2">
-        <v>61.58</v>
+        <v>43.9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E99" s="2">
         <v>-90</v>
@@ -2953,33 +2938,33 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="B100" s="2">
-        <v>38.15</v>
+        <v>38.495207000000001</v>
       </c>
       <c r="C100" s="2">
-        <v>57.75</v>
+        <v>46.452131000000001</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E100" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="B101" s="2">
-        <v>47.6</v>
+        <v>51.2</v>
       </c>
       <c r="C101" s="2">
-        <v>61.58</v>
+        <v>40.25</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E101" s="2">
         <v>-90</v>
@@ -2987,16 +2972,16 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="B102" s="2">
-        <v>45.25</v>
+        <v>53.5</v>
       </c>
       <c r="C102" s="2">
-        <v>62.4</v>
+        <v>40.25</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E102" s="2">
         <v>-90</v>
@@ -3004,135 +2989,135 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="B103" s="2">
-        <v>42.05</v>
+        <v>25.725000000000001</v>
       </c>
       <c r="C103" s="2">
-        <v>62.4</v>
+        <v>23</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E103" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="B104" s="2">
-        <v>32.774999999999999</v>
+        <v>72.47</v>
       </c>
       <c r="C104" s="2">
-        <v>69.290000000000006</v>
+        <v>42.63</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E104" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="B105" s="2">
-        <v>25.524999999999999</v>
+        <v>53.225000000000001</v>
       </c>
       <c r="C105" s="2">
-        <v>69.290000000000006</v>
+        <v>20.725000000000001</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E105" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="B106" s="2">
-        <v>27.941666000000001</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="C106" s="2">
-        <v>69.290000000000006</v>
+        <v>23</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E106" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="B107" s="2">
         <v>49.2</v>
       </c>
       <c r="C107" s="2">
-        <v>65.55</v>
+        <v>27.3</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E107" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="B108" s="2">
-        <v>30.358332000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C108" s="2">
-        <v>69.290000000000006</v>
+        <v>38.479999999999997</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E108" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="B109" s="2">
-        <v>44</v>
+        <v>68.58</v>
       </c>
       <c r="C109" s="2">
-        <v>65.95</v>
+        <v>42.92</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E109" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="B110" s="2">
-        <v>42.845207000000002</v>
+        <v>70.09</v>
       </c>
       <c r="C110" s="2">
-        <v>47.827131000000001</v>
+        <v>42.94</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E110" s="2">
         <v>90</v>
@@ -3140,16 +3125,16 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="B111" s="2">
-        <v>53.75</v>
+        <v>67.08</v>
       </c>
       <c r="C111" s="2">
-        <v>68</v>
+        <v>42.914999999999999</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E111" s="2">
         <v>90</v>
@@ -3157,16 +3142,16 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="B112" s="2">
-        <v>39.25</v>
+        <v>23.725000000000001</v>
       </c>
       <c r="C112" s="2">
-        <v>62.3</v>
+        <v>58.95</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E112" s="2">
         <v>90</v>
@@ -3174,118 +3159,118 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="B113" s="2">
-        <v>59.7</v>
+        <v>41</v>
       </c>
       <c r="C113" s="2">
-        <v>64.5</v>
+        <v>28.024999999999999</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E113" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="B114" s="2">
-        <v>26.387</v>
+        <v>60.711891999999999</v>
       </c>
       <c r="C114" s="2">
-        <v>58.475000000000001</v>
+        <v>41.491168999999999</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E114" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B115" s="2">
-        <v>68.3</v>
+        <v>57.141891999999999</v>
       </c>
       <c r="C115" s="2">
-        <v>65.150001000000003</v>
+        <v>50.561169</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E115" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="B116" s="2">
-        <v>8.99</v>
+        <v>60.486891999999997</v>
       </c>
       <c r="C116" s="2">
-        <v>67.73</v>
+        <v>45.566169000000002</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E116" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="B117" s="2">
-        <v>47.1</v>
+        <v>53.91</v>
       </c>
       <c r="C117" s="2">
-        <v>67.900000000000006</v>
+        <v>54.92</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E117" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="B118" s="2">
-        <v>54.052892</v>
+        <v>30.675000000000001</v>
       </c>
       <c r="C118" s="2">
-        <v>32.743169000000002</v>
+        <v>53.65</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E118" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="B119" s="2">
-        <v>41.195207000000003</v>
+        <v>30.65</v>
       </c>
       <c r="C119" s="2">
-        <v>41.327131000000001</v>
+        <v>56</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E119" s="2">
         <v>0</v>
@@ -3293,16 +3278,16 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="B120" s="2">
-        <v>69.3</v>
+        <v>30.65</v>
       </c>
       <c r="C120" s="2">
-        <v>33.543700000000001</v>
+        <v>58.3</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E120" s="2">
         <v>0</v>
@@ -3310,84 +3295,84 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="B121" s="2">
-        <v>50.191099999999999</v>
+        <v>57.55</v>
       </c>
       <c r="C121" s="2">
-        <v>45.563400000000001</v>
+        <v>62.65</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E121" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="B122" s="2">
-        <v>23.795207000000001</v>
+        <v>56.75</v>
       </c>
       <c r="C122" s="2">
-        <v>49.927131000000003</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E122" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="B123" s="2">
-        <v>60.02</v>
+        <v>60</v>
       </c>
       <c r="C123" s="2">
-        <v>55.987499999999997</v>
+        <v>61.8</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E123" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B124" s="2">
-        <v>56.342500000000001</v>
+        <v>53.35</v>
       </c>
       <c r="C124" s="2">
-        <v>54.45</v>
+        <v>65.81</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E124" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="B125" s="2">
-        <v>23.127400999999999</v>
+        <v>56.274999999999999</v>
       </c>
       <c r="C125" s="2">
-        <v>37.509900000000002</v>
+        <v>59.2</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E125" s="2">
         <v>180</v>
@@ -3395,16 +3380,16 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="B126" s="2">
-        <v>10.817500000000001</v>
+        <v>48.36</v>
       </c>
       <c r="C126" s="2">
-        <v>22.650001</v>
+        <v>58.575000000000003</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E126" s="2">
         <v>-90</v>
@@ -3412,84 +3397,84 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="B127" s="2">
-        <v>19.087499999999999</v>
+        <v>46.9</v>
       </c>
       <c r="C127" s="2">
-        <v>58.55</v>
+        <v>58.575000000000003</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E127" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="B128" s="2">
-        <v>6.34</v>
+        <v>44.55</v>
       </c>
       <c r="C128" s="2">
-        <v>44.1</v>
+        <v>57.75</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E128" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="B129" s="2">
-        <v>17.995207000000001</v>
+        <v>50.6</v>
       </c>
       <c r="C129" s="2">
-        <v>40.827131000000001</v>
+        <v>61.58</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E129" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="B130" s="2">
-        <v>17.996400000000001</v>
+        <v>41.35</v>
       </c>
       <c r="C130" s="2">
-        <v>39.827131000000001</v>
+        <v>57.75</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E130" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="B131" s="2">
-        <v>13.79</v>
+        <v>49.1</v>
       </c>
       <c r="C131" s="2">
-        <v>29.14</v>
+        <v>61.58</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E131" s="2">
         <v>-90</v>
@@ -3497,84 +3482,84 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="B132" s="2">
-        <v>30.6</v>
+        <v>38.15</v>
       </c>
       <c r="C132" s="2">
-        <v>30.3</v>
+        <v>57.75</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E132" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="B133" s="2">
-        <v>31.6</v>
+        <v>47.6</v>
       </c>
       <c r="C133" s="2">
-        <v>28.8</v>
+        <v>61.58</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E133" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="B134" s="2">
-        <v>19.482500000000002</v>
+        <v>45.25</v>
       </c>
       <c r="C134" s="2">
-        <v>61.09</v>
+        <v>62.4</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E134" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="B135" s="2">
-        <v>70.5</v>
+        <v>42.05</v>
       </c>
       <c r="C135" s="2">
-        <v>39.700000000000003</v>
+        <v>62.4</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E135" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="B136" s="2">
-        <v>24.145206999999999</v>
+        <v>32.774999999999999</v>
       </c>
       <c r="C136" s="2">
-        <v>30.402131000000001</v>
+        <v>69.290000000000006</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E136" s="2">
         <v>90</v>
@@ -3582,16 +3567,16 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="B137" s="2">
-        <v>68.7</v>
+        <v>25.524999999999999</v>
       </c>
       <c r="C137" s="2">
-        <v>19.912500000000001</v>
+        <v>69.290000000000006</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E137" s="2">
         <v>90</v>
@@ -3599,101 +3584,101 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="B138" s="2">
-        <v>30.6</v>
+        <v>27.941666000000001</v>
       </c>
       <c r="C138" s="2">
-        <v>33.325000000000003</v>
+        <v>69.290000000000006</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E138" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="B139" s="2">
-        <v>32.125</v>
+        <v>49.2</v>
       </c>
       <c r="C139" s="2">
-        <v>30.774999999999999</v>
+        <v>65.55</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E139" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="B140" s="2">
-        <v>46.709000000000003</v>
+        <v>30.358332000000001</v>
       </c>
       <c r="C140" s="2">
-        <v>48.342199999999998</v>
+        <v>69.290000000000006</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E140" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="B141" s="2">
-        <v>46.709000000000003</v>
+        <v>44</v>
       </c>
       <c r="C141" s="2">
-        <v>46.818199999999997</v>
+        <v>65.95</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E141" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="B142" s="2">
-        <v>49.759300000000003</v>
+        <v>42.845207000000002</v>
       </c>
       <c r="C142" s="2">
-        <v>48.078000000000003</v>
+        <v>47.827131000000001</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E142" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="B143" s="2">
-        <v>36.780892000000001</v>
+        <v>53.75</v>
       </c>
       <c r="C143" s="2">
-        <v>37.328169000000003</v>
+        <v>68</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E143" s="2">
         <v>90</v>
@@ -3701,33 +3686,33 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="B144" s="2">
-        <v>40.844892000000002</v>
+        <v>39.25</v>
       </c>
       <c r="C144" s="2">
-        <v>32.108168999999997</v>
+        <v>62.3</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E144" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="B145" s="2">
-        <v>40.844892000000002</v>
+        <v>59.7</v>
       </c>
       <c r="C145" s="2">
-        <v>33.632168999999998</v>
+        <v>64.5</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E145" s="2">
         <v>0</v>
@@ -3735,16 +3720,16 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="B146" s="2">
-        <v>18.5044</v>
+        <v>26.387</v>
       </c>
       <c r="C146" s="2">
-        <v>37.5137</v>
+        <v>58.475000000000001</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E146" s="2">
         <v>0</v>
@@ -3752,67 +3737,67 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="B147" s="2">
-        <v>27</v>
+        <v>68.3</v>
       </c>
       <c r="C147" s="2">
-        <v>41.125</v>
+        <v>65.150001000000003</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E147" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="B148" s="2">
-        <v>27.711400000000001</v>
+        <v>8.99</v>
       </c>
       <c r="C148" s="2">
-        <v>37.863199999999999</v>
+        <v>67.73</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E148" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="B149" s="2">
-        <v>32.11</v>
+        <v>47.1</v>
       </c>
       <c r="C149" s="2">
-        <v>9.1</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E149" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="B150" s="2">
-        <v>43.1</v>
+        <v>54.052892</v>
       </c>
       <c r="C150" s="2">
-        <v>15.2</v>
+        <v>32.743169000000002</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E150" s="2">
         <v>-90</v>
@@ -3820,16 +3805,16 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="B151" s="2">
-        <v>50.3</v>
+        <v>41.195207000000003</v>
       </c>
       <c r="C151" s="2">
-        <v>10.65</v>
+        <v>41.327131000000001</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E151" s="2">
         <v>0</v>
@@ -3837,101 +3822,101 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="B152" s="2">
-        <v>30.6</v>
+        <v>69.09</v>
       </c>
       <c r="C152" s="2">
-        <v>9.1</v>
+        <v>32.78</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E152" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="B153" s="2">
-        <v>31.8</v>
+        <v>50.191099999999999</v>
       </c>
       <c r="C153" s="2">
-        <v>15.525</v>
+        <v>45.563400000000001</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E153" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="B154" s="2">
-        <v>15.4948</v>
+        <v>23.795207000000001</v>
       </c>
       <c r="C154" s="2">
-        <v>49.296399999999998</v>
+        <v>49.927131000000003</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E154" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="B155" s="2">
-        <v>15.4948</v>
+        <v>60.02</v>
       </c>
       <c r="C155" s="2">
-        <v>46.248399999999997</v>
+        <v>55.987499999999997</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E155" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="B156" s="2">
-        <v>18.836400000000001</v>
+        <v>56.342500000000001</v>
       </c>
       <c r="C156" s="2">
-        <v>53.084099999999999</v>
+        <v>54.45</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E156" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="B157" s="2">
-        <v>19.398399999999999</v>
+        <v>23.127400999999999</v>
       </c>
       <c r="C157" s="2">
-        <v>55.557899999999997</v>
+        <v>37.509900000000002</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E157" s="2">
         <v>180</v>
@@ -3939,118 +3924,118 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="B158" s="2">
-        <v>20.359000000000002</v>
+        <v>10.817500000000001</v>
       </c>
       <c r="C158" s="2">
-        <v>53.084099999999999</v>
+        <v>22.650001</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E158" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="B159" s="2">
-        <v>23.154399999999999</v>
+        <v>19.087499999999999</v>
       </c>
       <c r="C159" s="2">
-        <v>46.213900000000002</v>
+        <v>58.55</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E159" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="B160" s="2">
-        <v>23.154399999999999</v>
+        <v>6.34</v>
       </c>
       <c r="C160" s="2">
-        <v>43.203499999999998</v>
+        <v>44.1</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E160" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="B161" s="2">
-        <v>24.6784</v>
+        <v>17.995207000000001</v>
       </c>
       <c r="C161" s="2">
-        <v>45.552131000000003</v>
+        <v>40.827131000000001</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E161" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="B162" s="2">
-        <v>31.788599000000001</v>
+        <v>17.996400000000001</v>
       </c>
       <c r="C162" s="2">
-        <v>50.693199999999997</v>
+        <v>39.827131000000001</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E162" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="B163" s="2">
-        <v>36.360599000000001</v>
+        <v>13.79</v>
       </c>
       <c r="C163" s="2">
-        <v>50.693199999999997</v>
+        <v>29.14</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E163" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="B164" s="2">
-        <v>60.136892000000003</v>
+        <v>30.6</v>
       </c>
       <c r="C164" s="2">
-        <v>51.691169000000002</v>
+        <v>30.3</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E164" s="2">
         <v>90</v>
@@ -4058,67 +4043,67 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="B165" s="2">
-        <v>52.439329000000001</v>
+        <v>31.6</v>
       </c>
       <c r="C165" s="2">
-        <v>53.53</v>
+        <v>28.8</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E165" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="B166" s="2">
-        <v>66.517799999999994</v>
+        <v>19.482500000000002</v>
       </c>
       <c r="C166" s="2">
-        <v>44.325000000000003</v>
+        <v>61.09</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E166" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="B167" s="2">
-        <v>50.479329</v>
+        <v>24.145206999999999</v>
       </c>
       <c r="C167" s="2">
-        <v>53.537500000000001</v>
+        <v>30.402131000000001</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E167" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="B168" s="2">
-        <v>63.469799999999999</v>
+        <v>68.7</v>
       </c>
       <c r="C168" s="2">
-        <v>44.655700000000003</v>
+        <v>19.912500000000001</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E168" s="2">
         <v>90</v>
@@ -4126,16 +4111,16 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="B169" s="2">
-        <v>31.91</v>
+        <v>30.6</v>
       </c>
       <c r="C169" s="2">
-        <v>66.950468999999998</v>
+        <v>33.325000000000003</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E169" s="2">
         <v>-90</v>
@@ -4143,101 +4128,101 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="B170" s="2">
-        <v>54.664999999999999</v>
+        <v>32.125</v>
       </c>
       <c r="C170" s="2">
-        <v>50.51</v>
+        <v>30.774999999999999</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E170" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="B171" s="2">
-        <v>56.136892000000003</v>
+        <v>46.709000000000003</v>
       </c>
       <c r="C171" s="2">
-        <v>41.491168999999999</v>
+        <v>48.342199999999998</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E171" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="B172" s="2">
-        <v>57.661892000000002</v>
+        <v>46.709000000000003</v>
       </c>
       <c r="C172" s="2">
-        <v>41.491168999999999</v>
+        <v>46.818199999999997</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E172" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="B173" s="2">
-        <v>59.186892</v>
+        <v>49.759300000000003</v>
       </c>
       <c r="C173" s="2">
-        <v>41.491168999999999</v>
+        <v>48.078000000000003</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E173" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="B174" s="2">
-        <v>60.486891999999997</v>
+        <v>36.780892000000001</v>
       </c>
       <c r="C174" s="2">
-        <v>44.041168999999996</v>
+        <v>37.328169000000003</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E174" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="B175" s="2">
-        <v>60.486891999999997</v>
+        <v>40.844892000000002</v>
       </c>
       <c r="C175" s="2">
-        <v>48.616168999999999</v>
+        <v>32.108168999999997</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E175" s="2">
         <v>0</v>
@@ -4245,16 +4230,16 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="B176" s="2">
-        <v>60.486891999999997</v>
+        <v>40.844892000000002</v>
       </c>
       <c r="C176" s="2">
-        <v>47.091169000000001</v>
+        <v>33.632168999999998</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E176" s="2">
         <v>0</v>
@@ -4262,50 +4247,50 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B177" s="2">
-        <v>56.73</v>
+        <v>18.5044</v>
       </c>
       <c r="C177" s="2">
-        <v>56.97</v>
+        <v>37.5137</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E177" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B178" s="2">
-        <v>42.15</v>
+        <v>27</v>
       </c>
       <c r="C178" s="2">
-        <v>52.398212999999998</v>
+        <v>41.125</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E178" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="B179" s="2">
-        <v>42.15</v>
+        <v>27.711400000000001</v>
       </c>
       <c r="C179" s="2">
-        <v>54.35</v>
+        <v>37.863199999999999</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E179" s="2">
         <v>180</v>
@@ -4313,16 +4298,16 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="B180" s="2">
-        <v>46.596891999999997</v>
+        <v>32.11</v>
       </c>
       <c r="C180" s="2">
-        <v>35.826169</v>
+        <v>9.1</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E180" s="2">
         <v>-90</v>
@@ -4330,16 +4315,16 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="B181" s="2">
-        <v>44.596891999999997</v>
+        <v>43.1</v>
       </c>
       <c r="C181" s="2">
-        <v>35.821168999999998</v>
+        <v>15.2</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E181" s="2">
         <v>-90</v>
@@ -4347,118 +4332,118 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="B182" s="2">
-        <v>52.43</v>
+        <v>50.3</v>
       </c>
       <c r="C182" s="2">
-        <v>26.3</v>
+        <v>10.65</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E182" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="B183" s="2">
-        <v>52.43</v>
+        <v>30.6</v>
       </c>
       <c r="C183" s="2">
-        <v>28.31</v>
+        <v>9.1</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E183" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2" t="s">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="B184" s="2">
-        <v>46.7</v>
+        <v>31.8</v>
       </c>
       <c r="C184" s="2">
-        <v>45.3</v>
+        <v>15.525</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E184" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="B185" s="2">
-        <v>26.65</v>
+        <v>15.4948</v>
       </c>
       <c r="C185" s="2">
-        <v>55.15</v>
+        <v>49.296399999999998</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E185" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="B186" s="2">
-        <v>26.637499999999999</v>
+        <v>15.4948</v>
       </c>
       <c r="C186" s="2">
-        <v>53.225000000000001</v>
+        <v>46.248399999999997</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E186" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="B187" s="2">
-        <v>29.4</v>
+        <v>18.836400000000001</v>
       </c>
       <c r="C187" s="2">
-        <v>51.35</v>
+        <v>53.084099999999999</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E187" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="B188" s="2">
-        <v>29.4</v>
+        <v>19.398399999999999</v>
       </c>
       <c r="C188" s="2">
-        <v>49.825000000000003</v>
+        <v>55.557899999999997</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E188" s="2">
         <v>180</v>
@@ -4466,16 +4451,16 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="B189" s="2">
-        <v>33.4</v>
+        <v>20.359000000000002</v>
       </c>
       <c r="C189" s="2">
-        <v>50.7</v>
+        <v>53.084099999999999</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E189" s="2">
         <v>90</v>
@@ -4483,67 +4468,67 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="B190" s="2">
-        <v>35.200000000000003</v>
+        <v>23.154399999999999</v>
       </c>
       <c r="C190" s="2">
-        <v>37.299999999999997</v>
+        <v>46.213900000000002</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E190" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="B191" s="2">
-        <v>71.400000000000006</v>
+        <v>23.154399999999999</v>
       </c>
       <c r="C191" s="2">
-        <v>47.5</v>
+        <v>43.203499999999998</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E191" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="B192" s="2">
-        <v>32.200000000000003</v>
+        <v>24.6784</v>
       </c>
       <c r="C192" s="2">
-        <v>33.799999999999997</v>
+        <v>45.552131000000003</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E192" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="B193" s="2">
-        <v>30.2</v>
+        <v>31.788599000000001</v>
       </c>
       <c r="C193" s="2">
-        <v>15.475</v>
+        <v>50.693199999999997</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E193" s="2">
         <v>-90</v>
@@ -4551,101 +4536,101 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2" t="s">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="B194" s="2">
-        <v>32.6</v>
+        <v>36.360599000000001</v>
       </c>
       <c r="C194" s="2">
-        <v>39.6</v>
+        <v>50.693199999999997</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E194" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2" t="s">
-        <v>197</v>
+        <v>162</v>
       </c>
       <c r="B195" s="2">
-        <v>30.2</v>
+        <v>60.136892000000003</v>
       </c>
       <c r="C195" s="2">
-        <v>12.4</v>
+        <v>51.691169000000002</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E195" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="B196" s="2">
-        <v>28.7</v>
+        <v>52.439329000000001</v>
       </c>
       <c r="C196" s="2">
-        <v>12.4</v>
+        <v>53.53</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E196" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="B197" s="2">
-        <v>60.2</v>
+        <v>50.479329</v>
       </c>
       <c r="C197" s="2">
-        <v>60.3</v>
+        <v>53.537500000000001</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E197" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2" t="s">
-        <v>200</v>
+        <v>165</v>
       </c>
       <c r="B198" s="2">
-        <v>69.599999999999994</v>
+        <v>31.91</v>
       </c>
       <c r="C198" s="2">
-        <v>44.524999999999999</v>
+        <v>66.950468999999998</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E198" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="B199" s="2">
-        <v>63.2</v>
+        <v>54.664999999999999</v>
       </c>
       <c r="C199" s="2">
-        <v>42.3</v>
+        <v>50.51</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E199" s="2">
         <v>180</v>
@@ -4653,33 +4638,33 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="B200" s="2">
-        <v>62.055</v>
+        <v>56.136892000000003</v>
       </c>
       <c r="C200" s="2">
-        <v>36.119999999999997</v>
+        <v>41.491168999999999</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E200" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="B201" s="2">
-        <v>73.849999999999994</v>
+        <v>57.661892000000002</v>
       </c>
       <c r="C201" s="2">
-        <v>44.725000000000001</v>
+        <v>41.491168999999999</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E201" s="2">
         <v>90</v>
@@ -4687,16 +4672,16 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="B202" s="2">
-        <v>55.5</v>
+        <v>59.186892</v>
       </c>
       <c r="C202" s="2">
-        <v>66.349999999999994</v>
+        <v>41.491168999999999</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E202" s="2">
         <v>90</v>
@@ -4704,118 +4689,118 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="B203" s="2">
-        <v>29.46</v>
+        <v>60.486891999999997</v>
       </c>
       <c r="C203" s="2">
-        <v>66.974999999999994</v>
+        <v>44.041168999999996</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E203" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="B204" s="2">
-        <v>54.4</v>
+        <v>60.486891999999997</v>
       </c>
       <c r="C204" s="2">
-        <v>63.2</v>
+        <v>48.616168999999999</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E204" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="B205" s="2">
-        <v>60.25</v>
+        <v>60.486891999999997</v>
       </c>
       <c r="C205" s="2">
-        <v>63.3</v>
+        <v>47.091169000000001</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E205" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="B206" s="2">
-        <v>54.3</v>
+        <v>56.73</v>
       </c>
       <c r="C206" s="2">
-        <v>65.790000000000006</v>
+        <v>56.97</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E206" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2" t="s">
-        <v>209</v>
+        <v>174</v>
       </c>
       <c r="B207" s="2">
-        <v>52.15</v>
+        <v>42.15</v>
       </c>
       <c r="C207" s="2">
-        <v>65.25</v>
+        <v>52.398212999999998</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E207" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="B208" s="2">
-        <v>55.65</v>
+        <v>42.15</v>
       </c>
       <c r="C208" s="2">
-        <v>61.85</v>
+        <v>54.35</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E208" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2" t="s">
-        <v>211</v>
+        <v>176</v>
       </c>
       <c r="B209" s="2">
-        <v>37.35</v>
+        <v>46.596891999999997</v>
       </c>
       <c r="C209" s="2">
-        <v>61.924999999999997</v>
+        <v>35.826169</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E209" s="2">
         <v>-90</v>
@@ -4823,16 +4808,16 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="B210" s="2">
-        <v>35.85</v>
+        <v>44.596891999999997</v>
       </c>
       <c r="C210" s="2">
-        <v>61.924999999999997</v>
+        <v>35.821168999999998</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E210" s="2">
         <v>-90</v>
@@ -4840,135 +4825,135 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="B211" s="2">
-        <v>34.35</v>
+        <v>52.43</v>
       </c>
       <c r="C211" s="2">
-        <v>61.924999999999997</v>
+        <v>26.3</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E211" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="B212" s="2">
-        <v>2.7</v>
+        <v>52.43</v>
       </c>
       <c r="C212" s="2">
-        <v>58.825000000000003</v>
+        <v>28.31</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E212" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2" t="s">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="B213" s="2">
-        <v>71.8</v>
+        <v>46.7</v>
       </c>
       <c r="C213" s="2">
-        <v>53</v>
+        <v>45.3</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E213" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="B214" s="2">
-        <v>54.45</v>
+        <v>26.65</v>
       </c>
       <c r="C214" s="2">
-        <v>61.3</v>
+        <v>55.15</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E214" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="B215" s="2">
-        <v>2.15</v>
+        <v>26.637499999999999</v>
       </c>
       <c r="C215" s="2">
-        <v>37.9</v>
+        <v>53.225000000000001</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E215" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="B216" s="2">
-        <v>2.15</v>
+        <v>29.4</v>
       </c>
       <c r="C216" s="2">
-        <v>42.1</v>
+        <v>51.35</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E216" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="B217" s="2">
-        <v>68.400000000000006</v>
+        <v>29.4</v>
       </c>
       <c r="C217" s="2">
-        <v>47.2</v>
+        <v>49.825000000000003</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E217" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="B218" s="2">
-        <v>12.3</v>
+        <v>33.4</v>
       </c>
       <c r="C218" s="2">
-        <v>49.3</v>
+        <v>50.7</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E218" s="2">
         <v>90</v>
@@ -4976,135 +4961,135 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="B219" s="2">
-        <v>2.65</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="C219" s="2">
-        <v>25</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E219" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="B220" s="2">
-        <v>2.15</v>
+        <v>71.400000000000006</v>
       </c>
       <c r="C220" s="2">
-        <v>35.799999999999997</v>
+        <v>47.5</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E220" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="B221" s="2">
-        <v>2.15</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="C221" s="2">
-        <v>40</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E221" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="B222" s="2">
-        <v>36.4</v>
+        <v>30.2</v>
       </c>
       <c r="C222" s="2">
-        <v>28.2</v>
+        <v>15.475</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E222" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="B223" s="2">
-        <v>38.799999999999997</v>
+        <v>32.6</v>
       </c>
       <c r="C223" s="2">
-        <v>28.2</v>
+        <v>39.6</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E223" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2" t="s">
-        <v>226</v>
+        <v>191</v>
       </c>
       <c r="B224" s="2">
-        <v>78</v>
+        <v>30.2</v>
       </c>
       <c r="C224" s="2">
-        <v>66.099999999999994</v>
+        <v>12.4</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E224" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="2" t="s">
-        <v>227</v>
+        <v>192</v>
       </c>
       <c r="B225" s="2">
-        <v>75.650000000000006</v>
+        <v>28.7</v>
       </c>
       <c r="C225" s="2">
-        <v>66.099999999999994</v>
+        <v>12.4</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E225" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="2" t="s">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="B226" s="2">
-        <v>77.8</v>
+        <v>60.2</v>
       </c>
       <c r="C226" s="2">
-        <v>68.599999999999994</v>
+        <v>60.3</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E226" s="2">
         <v>0</v>
@@ -5112,50 +5097,50 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="2" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="B227" s="2">
-        <v>75.7</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="C227" s="2">
-        <v>68.599999999999994</v>
+        <v>45.3</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E227" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="B228" s="2">
-        <v>2.65</v>
+        <v>72.375</v>
       </c>
       <c r="C228" s="2">
-        <v>27.15</v>
+        <v>37.26</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E228" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="2" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="B229" s="2">
-        <v>23.03</v>
+        <v>64.8</v>
       </c>
       <c r="C229" s="2">
-        <v>41.36</v>
+        <v>42.12</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E229" s="2">
         <v>180</v>
@@ -5163,84 +5148,84 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="2" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="B230" s="2">
-        <v>20.8</v>
+        <v>55.5</v>
       </c>
       <c r="C230" s="2">
-        <v>41.2</v>
+        <v>66.349999999999994</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E230" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="2" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="B231" s="2">
-        <v>6.75</v>
+        <v>29.46</v>
       </c>
       <c r="C231" s="2">
-        <v>61.1</v>
+        <v>66.974999999999994</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E231" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="2" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="B232" s="2">
-        <v>27.75</v>
+        <v>54.4</v>
       </c>
       <c r="C232" s="2">
-        <v>61.15</v>
+        <v>63.2</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E232" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="2" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="B233" s="2">
-        <v>56.8</v>
+        <v>60.25</v>
       </c>
       <c r="C233" s="2">
-        <v>38.429504999999999</v>
+        <v>63.3</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E233" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="2" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="B234" s="2">
-        <v>13.4</v>
+        <v>54.3</v>
       </c>
       <c r="C234" s="2">
-        <v>45.1</v>
+        <v>65.790000000000006</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E234" s="2">
         <v>90</v>
@@ -5248,135 +5233,135 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="2" t="s">
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="B235" s="2">
-        <v>59.9</v>
+        <v>52.15</v>
       </c>
       <c r="C235" s="2">
-        <v>38.450000000000003</v>
+        <v>65.25</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E235" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="2" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="B236" s="2">
-        <v>22.74</v>
+        <v>55.65</v>
       </c>
       <c r="C236" s="2">
-        <v>67.459999999999994</v>
+        <v>61.85</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E236" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="2" t="s">
-        <v>239</v>
+        <v>204</v>
       </c>
       <c r="B237" s="2">
-        <v>75.55</v>
+        <v>37.35</v>
       </c>
       <c r="C237" s="2">
-        <v>41.1</v>
+        <v>61.924999999999997</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E237" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="2" t="s">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="B238" s="2">
-        <v>64.650000000000006</v>
+        <v>35.85</v>
       </c>
       <c r="C238" s="2">
-        <v>24.8</v>
+        <v>61.924999999999997</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E238" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="2" t="s">
-        <v>241</v>
+        <v>206</v>
       </c>
       <c r="B239" s="2">
-        <v>4.4000000000000004</v>
+        <v>34.35</v>
       </c>
       <c r="C239" s="2">
-        <v>17.5</v>
+        <v>61.924999999999997</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E239" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="2" t="s">
-        <v>242</v>
+        <v>207</v>
       </c>
       <c r="B240" s="2">
-        <v>59.35</v>
+        <v>2.7</v>
       </c>
       <c r="C240" s="2">
-        <v>24.75</v>
+        <v>58.825000000000003</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E240" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="2" t="s">
-        <v>243</v>
+        <v>208</v>
       </c>
       <c r="B241" s="2">
-        <v>52.65</v>
+        <v>71.8</v>
       </c>
       <c r="C241" s="2">
-        <v>59.91</v>
+        <v>53</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E241" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="2" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
       <c r="B242" s="2">
-        <v>8.2891929999999991</v>
+        <v>54.45</v>
       </c>
       <c r="C242" s="2">
-        <v>49.317568999999999</v>
+        <v>61.3</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E242" s="2">
         <v>90</v>
@@ -5384,50 +5369,50 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="2" t="s">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="B243" s="2">
-        <v>11.900399999999999</v>
+        <v>2.15</v>
       </c>
       <c r="C243" s="2">
-        <v>36.243699999999997</v>
+        <v>37.9</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E243" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="2" t="s">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="B244" s="2">
-        <v>47.09</v>
+        <v>2.15</v>
       </c>
       <c r="C244" s="2">
-        <v>51.044800000000002</v>
+        <v>42.1</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E244" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="2" t="s">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="B245" s="2">
-        <v>37.542892000000002</v>
+        <v>68.400000000000006</v>
       </c>
       <c r="C245" s="2">
-        <v>32.806668999999999</v>
+        <v>47.2</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E245" s="2">
         <v>90</v>
@@ -5435,118 +5420,118 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="2" t="s">
-        <v>248</v>
+        <v>213</v>
       </c>
       <c r="B246" s="2">
-        <v>45.543892</v>
+        <v>12.3</v>
       </c>
       <c r="C246" s="2">
-        <v>32.743169000000002</v>
+        <v>49.3</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E246" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="2" t="s">
-        <v>249</v>
+        <v>214</v>
       </c>
       <c r="B247" s="2">
-        <v>26.31</v>
+        <v>2.65</v>
       </c>
       <c r="C247" s="2">
-        <v>65.83</v>
+        <v>25</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E247" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="2" t="s">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="B248" s="2">
-        <v>46.174999999999997</v>
+        <v>2.15</v>
       </c>
       <c r="C248" s="2">
-        <v>13.4</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E248" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="2" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="B249" s="2">
-        <v>34.9</v>
+        <v>2.15</v>
       </c>
       <c r="C249" s="2">
-        <v>13.1</v>
+        <v>40</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E249" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="2" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="B250" s="2">
-        <v>19.774799999999999</v>
+        <v>36.4</v>
       </c>
       <c r="C250" s="2">
-        <v>47.496400000000001</v>
+        <v>28.2</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E250" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="2" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="B251" s="2">
-        <v>34.430199000000002</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="C251" s="2">
-        <v>45.816400000000002</v>
+        <v>28.2</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E251" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="2" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="B252" s="2">
-        <v>67.116799999999998</v>
+        <v>78</v>
       </c>
       <c r="C252" s="2">
-        <v>40.439700000000002</v>
+        <v>66.099999999999994</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E252" s="2">
         <v>0</v>
@@ -5554,16 +5539,16 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="2" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="B253" s="2">
-        <v>55.611891999999997</v>
+        <v>75.650000000000006</v>
       </c>
       <c r="C253" s="2">
-        <v>46.441169000000002</v>
+        <v>66.099999999999994</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E253" s="2">
         <v>0</v>
@@ -5571,118 +5556,118 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="2" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="B254" s="2">
-        <v>65.75</v>
+        <v>77.8</v>
       </c>
       <c r="C254" s="2">
-        <v>47.15</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E254" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="2" t="s">
-        <v>257</v>
+        <v>222</v>
       </c>
       <c r="B255" s="2">
-        <v>11.82</v>
+        <v>75.7</v>
       </c>
       <c r="C255" s="2">
-        <v>29.12</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E255" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="B256" s="2">
-        <v>40</v>
+        <v>2.65</v>
       </c>
       <c r="C256" s="2">
-        <v>50.164999999999999</v>
+        <v>27.15</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E256" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="2" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="B257" s="2">
-        <v>13.495207000000001</v>
+        <v>23.03</v>
       </c>
       <c r="C257" s="2">
-        <v>34.016168999999998</v>
+        <v>41.36</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E257" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="2" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="B258" s="2">
-        <v>9.1</v>
+        <v>20.8</v>
       </c>
       <c r="C258" s="2">
-        <v>40.5</v>
+        <v>41.2</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E258" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="2" t="s">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="B259" s="2">
-        <v>10.595207</v>
+        <v>6.75</v>
       </c>
       <c r="C259" s="2">
-        <v>34.016168999999998</v>
+        <v>61.1</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E259" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="2" t="s">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="B260" s="2">
-        <v>8.4</v>
+        <v>27.75</v>
       </c>
       <c r="C260" s="2">
-        <v>38.700000000000003</v>
+        <v>61.15</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E260" s="2">
         <v>0</v>
@@ -5690,16 +5675,16 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="2" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="B261" s="2">
-        <v>70.75</v>
+        <v>56.8</v>
       </c>
       <c r="C261" s="2">
-        <v>59.25</v>
+        <v>38.429504999999999</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E261" s="2">
         <v>0</v>
@@ -5707,254 +5692,254 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="2" t="s">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="B262" s="2">
-        <v>65.27</v>
+        <v>13.4</v>
       </c>
       <c r="C262" s="2">
-        <v>59.25</v>
+        <v>45.1</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E262" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="2" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="B263" s="2">
-        <v>18.2</v>
+        <v>59.9</v>
       </c>
       <c r="C263" s="2">
-        <v>39.1</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E263" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="2" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="B264" s="2">
-        <v>53.75</v>
+        <v>22.74</v>
       </c>
       <c r="C264" s="2">
-        <v>67.38</v>
+        <v>67.459999999999994</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E264" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="2" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="B265" s="2">
-        <v>57.55</v>
+        <v>75.55</v>
       </c>
       <c r="C265" s="2">
-        <v>67.38</v>
+        <v>41.1</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E265" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="2" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="B266" s="2">
-        <v>52.45</v>
+        <v>64.650000000000006</v>
       </c>
       <c r="C266" s="2">
-        <v>65.525000000000006</v>
+        <v>24.8</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E266" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="2" t="s">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="B267" s="2">
-        <v>54.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="C267" s="2">
-        <v>67.38</v>
+        <v>17.5</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E267" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="2" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="B268" s="2">
-        <v>53.4</v>
+        <v>59.35</v>
       </c>
       <c r="C268" s="2">
-        <v>65.525000000000006</v>
+        <v>24.75</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E268" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="2" t="s">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="B269" s="2">
-        <v>47.55</v>
+        <v>52.65</v>
       </c>
       <c r="C269" s="2">
-        <v>65.55</v>
+        <v>59.91</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E269" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="2" t="s">
-        <v>273</v>
+        <v>237</v>
       </c>
       <c r="B270" s="2">
-        <v>56.6</v>
+        <v>8.2891929999999991</v>
       </c>
       <c r="C270" s="2">
-        <v>67.38</v>
+        <v>49.317568999999999</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E270" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="2" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="B271" s="2">
-        <v>46.6</v>
+        <v>11.900399999999999</v>
       </c>
       <c r="C271" s="2">
-        <v>65.55</v>
+        <v>36.243699999999997</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E271" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="2" t="s">
-        <v>275</v>
+        <v>239</v>
       </c>
       <c r="B272" s="2">
-        <v>55.65</v>
+        <v>47.09</v>
       </c>
       <c r="C272" s="2">
-        <v>67.38</v>
+        <v>51.044800000000002</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E272" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="2" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="B273" s="2">
-        <v>51.5</v>
+        <v>37.542892000000002</v>
       </c>
       <c r="C273" s="2">
-        <v>65.55</v>
+        <v>32.806668999999999</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E273" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="2" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
       <c r="B274" s="2">
-        <v>45.65</v>
+        <v>45.543892</v>
       </c>
       <c r="C274" s="2">
-        <v>65.55</v>
+        <v>32.743169000000002</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E274" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="2" t="s">
-        <v>278</v>
+        <v>242</v>
       </c>
       <c r="B275" s="2">
-        <v>55.45</v>
+        <v>26.31</v>
       </c>
       <c r="C275" s="2">
-        <v>59.5</v>
+        <v>65.83</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E275" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="2" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="B276" s="2">
-        <v>57.3</v>
+        <v>46.174999999999997</v>
       </c>
       <c r="C276" s="2">
-        <v>61.45</v>
+        <v>13.4</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E276" s="2">
         <v>180</v>
@@ -5962,16 +5947,16 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="2" t="s">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="B277" s="2">
-        <v>54.9</v>
+        <v>34.9</v>
       </c>
       <c r="C277" s="2">
-        <v>58.3</v>
+        <v>13.1</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E277" s="2">
         <v>180</v>
@@ -5979,207 +5964,157 @@
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="2" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B278" s="2">
-        <v>54.35</v>
+        <v>68.72</v>
       </c>
       <c r="C278" s="2">
-        <v>65.525000000000006</v>
+        <v>38.74</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E278" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="2" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B279" s="2">
-        <v>33.5</v>
+        <v>73.59</v>
       </c>
       <c r="C279" s="2">
-        <v>27.824999999999999</v>
+        <v>44.697499999999998</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E279" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="2" t="s">
-        <v>283</v>
+        <v>245</v>
       </c>
       <c r="B280" s="2">
-        <v>40</v>
+        <v>19.774799999999999</v>
       </c>
       <c r="C280" s="2">
-        <v>7.15</v>
+        <v>47.496400000000001</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E280" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="2" t="s">
-        <v>284</v>
+        <v>246</v>
       </c>
       <c r="B281" s="2">
-        <v>46.5</v>
+        <v>34.430199000000002</v>
       </c>
       <c r="C281" s="2">
-        <v>27.824999999999999</v>
+        <v>45.816400000000002</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E281" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="2" t="s">
-        <v>285</v>
+        <v>247</v>
       </c>
       <c r="B282" s="2">
-        <v>39.9</v>
+        <v>55.611891999999997</v>
       </c>
       <c r="C282" s="2">
-        <v>15.6</v>
+        <v>46.441169000000002</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E282" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="2" t="s">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="B283" s="2">
-        <v>21.8</v>
+        <v>65.75</v>
       </c>
       <c r="C283" s="2">
-        <v>39.1</v>
+        <v>47.15</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E283" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="2" t="s">
-        <v>287</v>
+        <v>249</v>
       </c>
       <c r="B284" s="2">
-        <v>63.075000000000003</v>
+        <v>11.82</v>
       </c>
       <c r="C284" s="2">
-        <v>38.700000000000003</v>
+        <v>29.12</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E284" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="285" spans="1:5">
-      <c r="A285" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="B285" s="2">
-        <v>40</v>
-      </c>
-      <c r="C285" s="2">
-        <v>29.824999999999999</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E285" s="2">
-        <v>90</v>
-      </c>
+      <c r="A285" s="2"/>
+      <c r="B285" s="2"/>
+      <c r="C285" s="2"/>
+      <c r="D285" s="2"/>
+      <c r="E285" s="2"/>
     </row>
     <row r="286" spans="1:5">
-      <c r="A286" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B286" s="2">
-        <v>70.650000000000006</v>
-      </c>
-      <c r="C286" s="2">
-        <v>60.15</v>
-      </c>
-      <c r="D286" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E286" s="2">
-        <v>0</v>
-      </c>
+      <c r="A286" s="2"/>
+      <c r="B286" s="2"/>
+      <c r="C286" s="2"/>
+      <c r="D286" s="2"/>
+      <c r="E286" s="2"/>
     </row>
     <row r="287" spans="1:5">
-      <c r="A287" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="B287" s="2">
-        <v>65.8</v>
-      </c>
-      <c r="C287" s="2">
-        <v>60.15</v>
-      </c>
-      <c r="D287" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E287" s="2">
-        <v>180</v>
-      </c>
+      <c r="A287" s="2"/>
+      <c r="B287" s="2"/>
+      <c r="C287" s="2"/>
+      <c r="D287" s="2"/>
+      <c r="E287" s="2"/>
     </row>
     <row r="288" spans="1:5">
-      <c r="A288" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B288" s="2">
-        <v>70.8</v>
-      </c>
-      <c r="C288" s="2">
-        <v>61.95</v>
-      </c>
-      <c r="D288" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E288" s="2">
-        <v>0</v>
-      </c>
+      <c r="A288" s="2"/>
+      <c r="B288" s="2"/>
+      <c r="C288" s="2"/>
+      <c r="D288" s="2"/>
+      <c r="E288" s="2"/>
     </row>
     <row r="289" spans="1:5">
-      <c r="A289" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B289" s="2">
-        <v>66.3</v>
-      </c>
-      <c r="C289" s="2">
-        <v>61.95</v>
-      </c>
-      <c r="D289" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E289" s="2">
-        <v>180</v>
-      </c>
+      <c r="A289" s="2"/>
+      <c r="B289" s="2"/>
+      <c r="C289" s="2"/>
+      <c r="D289" s="2"/>
+      <c r="E289" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pcb/robot/gerbers/POS_JLCPCB.xlsx
+++ b/pcb/robot/gerbers/POS_JLCPCB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JHORDAN\FREELANCE\PROYECTOS\KICAD_USB_PD_MODULAR\Github\smartphone-robot-cad\pcb\robot\gerbers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F882ECDE-7E0D-42B2-90BD-343C79F6A25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54487A54-8183-4341-B44D-67FD01E31379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="384">
   <si>
     <t>Designator</t>
   </si>
@@ -330,12 +330,6 @@
     <t>C136</t>
   </si>
   <si>
-    <t>C137</t>
-  </si>
-  <si>
-    <t>C138</t>
-  </si>
-  <si>
     <t>D1</t>
   </si>
   <si>
@@ -372,12 +366,6 @@
     <t>J1</t>
   </si>
   <si>
-    <t>J2</t>
-  </si>
-  <si>
-    <t>J8</t>
-  </si>
-  <si>
     <t>L1</t>
   </si>
   <si>
@@ -612,9 +600,6 @@
     <t>R91</t>
   </si>
   <si>
-    <t>R92</t>
-  </si>
-  <si>
     <t>R94</t>
   </si>
   <si>
@@ -651,9 +636,6 @@
     <t>S2</t>
   </si>
   <si>
-    <t>S3</t>
-  </si>
-  <si>
     <t>TH2</t>
   </si>
   <si>
@@ -711,30 +693,12 @@
     <t>TP29</t>
   </si>
   <si>
-    <t>TP30</t>
-  </si>
-  <si>
     <t>TP33</t>
   </si>
   <si>
     <t>TP34</t>
   </si>
   <si>
-    <t>TP39</t>
-  </si>
-  <si>
-    <t>TP40</t>
-  </si>
-  <si>
-    <t>TP41</t>
-  </si>
-  <si>
-    <t>TP42</t>
-  </si>
-  <si>
-    <t>TP43</t>
-  </si>
-  <si>
     <t>U1</t>
   </si>
   <si>
@@ -780,9 +744,6 @@
     <t>top</t>
   </si>
   <si>
-    <t>BT1</t>
-  </si>
-  <si>
     <t>C7</t>
   </si>
   <si>
@@ -804,97 +765,418 @@
     <t>C37</t>
   </si>
   <si>
+    <t>C114</t>
+  </si>
+  <si>
+    <t>C115</t>
+  </si>
+  <si>
+    <t>C116</t>
+  </si>
+  <si>
+    <t>C117</t>
+  </si>
+  <si>
+    <t>C118</t>
+  </si>
+  <si>
+    <t>C119</t>
+  </si>
+  <si>
+    <t>C120</t>
+  </si>
+  <si>
+    <t>C121</t>
+  </si>
+  <si>
+    <t>C122</t>
+  </si>
+  <si>
+    <t>C123</t>
+  </si>
+  <si>
+    <t>C124</t>
+  </si>
+  <si>
+    <t>C125</t>
+  </si>
+  <si>
+    <t>C126</t>
+  </si>
+  <si>
+    <t>C128</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>J9</t>
+  </si>
+  <si>
+    <t>R23</t>
+  </si>
+  <si>
+    <t>R90</t>
+  </si>
+  <si>
+    <t>SW1</t>
+  </si>
+  <si>
+    <t>U26</t>
+  </si>
+  <si>
+    <t>U27</t>
+  </si>
+  <si>
+    <t>U28</t>
+  </si>
+  <si>
+    <t>U29</t>
+  </si>
+  <si>
+    <t>bottom</t>
+  </si>
+  <si>
+    <t>C45</t>
+  </si>
+  <si>
+    <t>C46</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>U11</t>
+  </si>
+  <si>
+    <t>BT2</t>
+  </si>
+  <si>
+    <t>C81</t>
+  </si>
+  <si>
+    <t>C84</t>
+  </si>
+  <si>
+    <t>C85</t>
+  </si>
+  <si>
+    <t>J6</t>
+  </si>
+  <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>R120</t>
+  </si>
+  <si>
+    <t>U15</t>
+  </si>
+  <si>
+    <t>U17</t>
+  </si>
+  <si>
+    <t>U19</t>
+  </si>
+  <si>
+    <t>C47</t>
+  </si>
+  <si>
+    <t>C48</t>
+  </si>
+  <si>
+    <t>C49</t>
+  </si>
+  <si>
+    <t>C50</t>
+  </si>
+  <si>
+    <t>C51</t>
+  </si>
+  <si>
+    <t>C52</t>
+  </si>
+  <si>
+    <t>C53</t>
+  </si>
+  <si>
+    <t>C54</t>
+  </si>
+  <si>
+    <t>C87</t>
+  </si>
+  <si>
+    <t>C97</t>
+  </si>
+  <si>
+    <t>C98</t>
+  </si>
+  <si>
+    <t>C100</t>
+  </si>
+  <si>
+    <t>C101</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>L5</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>R26</t>
+  </si>
+  <si>
+    <t>R32</t>
+  </si>
+  <si>
+    <t>R33</t>
+  </si>
+  <si>
+    <t>R34</t>
+  </si>
+  <si>
+    <t>R35</t>
+  </si>
+  <si>
+    <t>R36</t>
+  </si>
+  <si>
+    <t>R37</t>
+  </si>
+  <si>
+    <t>R38</t>
+  </si>
+  <si>
+    <t>R39</t>
+  </si>
+  <si>
+    <t>R40</t>
+  </si>
+  <si>
+    <t>R53</t>
+  </si>
+  <si>
+    <t>R55</t>
+  </si>
+  <si>
+    <t>R57</t>
+  </si>
+  <si>
+    <t>R65</t>
+  </si>
+  <si>
+    <t>R73</t>
+  </si>
+  <si>
+    <t>R74</t>
+  </si>
+  <si>
+    <t>R75</t>
+  </si>
+  <si>
+    <t>R93</t>
+  </si>
+  <si>
+    <t>R95</t>
+  </si>
+  <si>
+    <t>R106</t>
+  </si>
+  <si>
+    <t>R107</t>
+  </si>
+  <si>
+    <t>R108</t>
+  </si>
+  <si>
+    <t>R109</t>
+  </si>
+  <si>
+    <t>R110</t>
+  </si>
+  <si>
+    <t>R111</t>
+  </si>
+  <si>
+    <t>R112</t>
+  </si>
+  <si>
+    <t>R113</t>
+  </si>
+  <si>
+    <t>R114</t>
+  </si>
+  <si>
+    <t>R115</t>
+  </si>
+  <si>
+    <t>R116</t>
+  </si>
+  <si>
+    <t>R117</t>
+  </si>
+  <si>
+    <t>R118</t>
+  </si>
+  <si>
+    <t>R119</t>
+  </si>
+  <si>
+    <t>R121</t>
+  </si>
+  <si>
+    <t>R122</t>
+  </si>
+  <si>
+    <t>R123</t>
+  </si>
+  <si>
+    <t>R124</t>
+  </si>
+  <si>
+    <t>R125</t>
+  </si>
+  <si>
+    <t>R126</t>
+  </si>
+  <si>
+    <t>R127</t>
+  </si>
+  <si>
+    <t>R128</t>
+  </si>
+  <si>
+    <t>R129</t>
+  </si>
+  <si>
+    <t>R130</t>
+  </si>
+  <si>
+    <t>R131</t>
+  </si>
+  <si>
+    <t>R132</t>
+  </si>
+  <si>
+    <t>R133</t>
+  </si>
+  <si>
+    <t>R134</t>
+  </si>
+  <si>
+    <t>R135</t>
+  </si>
+  <si>
+    <t>R136</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>S4</t>
+  </si>
+  <si>
+    <t>TP3</t>
+  </si>
+  <si>
+    <t>TP4</t>
+  </si>
+  <si>
+    <t>TP5</t>
+  </si>
+  <si>
+    <t>TP6</t>
+  </si>
+  <si>
+    <t>TP7</t>
+  </si>
+  <si>
+    <t>TP8</t>
+  </si>
+  <si>
+    <t>TP12</t>
+  </si>
+  <si>
+    <t>TP13</t>
+  </si>
+  <si>
+    <t>TP14</t>
+  </si>
+  <si>
+    <t>TP15</t>
+  </si>
+  <si>
+    <t>TP25</t>
+  </si>
+  <si>
+    <t>TP31</t>
+  </si>
+  <si>
+    <t>TP32</t>
+  </si>
+  <si>
+    <t>TP35</t>
+  </si>
+  <si>
+    <t>TP36</t>
+  </si>
+  <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>U16</t>
+  </si>
+  <si>
+    <t>U20</t>
+  </si>
+  <si>
+    <t>U21</t>
+  </si>
+  <si>
+    <t>U22</t>
+  </si>
+  <si>
+    <t>U23</t>
+  </si>
+  <si>
+    <t>U24</t>
+  </si>
+  <si>
+    <t>U30</t>
+  </si>
+  <si>
+    <t>U31</t>
+  </si>
+  <si>
+    <t>U32</t>
+  </si>
+  <si>
+    <t>U33</t>
+  </si>
+  <si>
+    <t>U34</t>
+  </si>
+  <si>
     <t>C113</t>
-  </si>
-  <si>
-    <t>C114</t>
-  </si>
-  <si>
-    <t>C115</t>
-  </si>
-  <si>
-    <t>C116</t>
-  </si>
-  <si>
-    <t>C117</t>
-  </si>
-  <si>
-    <t>C118</t>
-  </si>
-  <si>
-    <t>C119</t>
-  </si>
-  <si>
-    <t>C120</t>
-  </si>
-  <si>
-    <t>C121</t>
-  </si>
-  <si>
-    <t>C122</t>
-  </si>
-  <si>
-    <t>C123</t>
-  </si>
-  <si>
-    <t>C124</t>
-  </si>
-  <si>
-    <t>C125</t>
-  </si>
-  <si>
-    <t>C126</t>
-  </si>
-  <si>
-    <t>C128</t>
-  </si>
-  <si>
-    <t>J3</t>
-  </si>
-  <si>
-    <t>J4</t>
-  </si>
-  <si>
-    <t>J5</t>
-  </si>
-  <si>
-    <t>J9</t>
-  </si>
-  <si>
-    <t>R23</t>
-  </si>
-  <si>
-    <t>R90</t>
-  </si>
-  <si>
-    <t>SW1</t>
-  </si>
-  <si>
-    <t>U26</t>
-  </si>
-  <si>
-    <t>U27</t>
-  </si>
-  <si>
-    <t>U28</t>
-  </si>
-  <si>
-    <t>U29</t>
-  </si>
-  <si>
-    <t>bottom</t>
-  </si>
-  <si>
-    <t>C45</t>
-  </si>
-  <si>
-    <t>C46</t>
-  </si>
-  <si>
-    <t>U10</t>
-  </si>
-  <si>
-    <t>U11</t>
   </si>
 </sst>
 </file>
@@ -1243,7 +1525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E289"/>
+  <dimension ref="A1:E378"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
@@ -1272,16 +1554,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="B2" s="2">
-        <v>40</v>
+        <v>70.75</v>
       </c>
       <c r="C2" s="2">
-        <v>50.164999999999999</v>
+        <v>59.25</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E2" s="2">
         <v>0</v>
@@ -1289,118 +1571,118 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>252</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2">
-        <v>13.495207000000001</v>
+        <v>65.27</v>
       </c>
       <c r="C3" s="2">
-        <v>34.016168999999998</v>
+        <v>59.25</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E3" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>253</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2">
-        <v>9.1</v>
+        <v>53.75</v>
       </c>
       <c r="C4" s="2">
-        <v>40.5</v>
+        <v>67.38</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>254</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2">
-        <v>10.595207</v>
+        <v>57.55</v>
       </c>
       <c r="C5" s="2">
-        <v>34.016168999999998</v>
+        <v>67.38</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E5" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>255</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2">
-        <v>8.4</v>
+        <v>52.45</v>
       </c>
       <c r="C6" s="2">
-        <v>38.700000000000003</v>
+        <v>65.525000000000006</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E6" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>256</v>
+        <v>60</v>
       </c>
       <c r="B7" s="2">
-        <v>70.75</v>
+        <v>54.7</v>
       </c>
       <c r="C7" s="2">
-        <v>59.25</v>
+        <v>67.38</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>257</v>
+        <v>63</v>
       </c>
       <c r="B8" s="2">
-        <v>65.27</v>
+        <v>53.4</v>
       </c>
       <c r="C8" s="2">
-        <v>59.25</v>
+        <v>65.525000000000006</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E8" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>258</v>
+        <v>65</v>
       </c>
       <c r="B9" s="2">
-        <v>18.2</v>
+        <v>47.55</v>
       </c>
       <c r="C9" s="2">
-        <v>39.1</v>
+        <v>65.55</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E9" s="2">
         <v>90</v>
@@ -1408,16 +1690,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>259</v>
+        <v>66</v>
       </c>
       <c r="B10" s="2">
-        <v>53.75</v>
+        <v>56.6</v>
       </c>
       <c r="C10" s="2">
         <v>67.38</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E10" s="2">
         <v>-90</v>
@@ -1425,50 +1707,50 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>260</v>
+        <v>67</v>
       </c>
       <c r="B11" s="2">
-        <v>57.55</v>
+        <v>46.6</v>
       </c>
       <c r="C11" s="2">
-        <v>67.38</v>
+        <v>65.55</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E11" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B12" s="2">
-        <v>52.45</v>
+        <v>55.65</v>
       </c>
       <c r="C12" s="2">
-        <v>65.525000000000006</v>
+        <v>67.38</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E12" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B13" s="2">
-        <v>54.7</v>
+        <v>51.5</v>
       </c>
       <c r="C13" s="2">
-        <v>67.38</v>
+        <v>65.55</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E13" s="2">
         <v>-90</v>
@@ -1476,16 +1758,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="B14" s="2">
-        <v>53.4</v>
+        <v>45.65</v>
       </c>
       <c r="C14" s="2">
-        <v>65.525000000000006</v>
+        <v>65.55</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E14" s="2">
         <v>90</v>
@@ -1493,118 +1775,118 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>264</v>
+        <v>71</v>
       </c>
       <c r="B15" s="2">
-        <v>47.55</v>
+        <v>55.45</v>
       </c>
       <c r="C15" s="2">
-        <v>65.55</v>
+        <v>59.5</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E15" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>265</v>
+        <v>74</v>
       </c>
       <c r="B16" s="2">
-        <v>56.6</v>
+        <v>57.3</v>
       </c>
       <c r="C16" s="2">
-        <v>67.38</v>
+        <v>61.45</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E16" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>266</v>
+        <v>75</v>
       </c>
       <c r="B17" s="2">
-        <v>46.6</v>
+        <v>54.9</v>
       </c>
       <c r="C17" s="2">
-        <v>65.55</v>
+        <v>58.3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E17" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>267</v>
+        <v>76</v>
       </c>
       <c r="B18" s="2">
-        <v>55.65</v>
+        <v>54.35</v>
       </c>
       <c r="C18" s="2">
-        <v>67.38</v>
+        <v>65.525000000000006</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E18" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>268</v>
+        <v>78</v>
       </c>
       <c r="B19" s="2">
-        <v>51.5</v>
+        <v>13.495207000000001</v>
       </c>
       <c r="C19" s="2">
-        <v>65.55</v>
+        <v>34.016168999999998</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E19" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2">
-        <v>45.65</v>
+        <v>9.1</v>
       </c>
       <c r="C20" s="2">
-        <v>65.55</v>
+        <v>40.5</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E20" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B21" s="2">
+        <v>10.595207</v>
+      </c>
+      <c r="C21" s="2">
+        <v>34.016168999999998</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="B21" s="2">
-        <v>55.45</v>
-      </c>
-      <c r="C21" s="2">
-        <v>59.5</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="E21" s="2">
         <v>180</v>
@@ -1612,33 +1894,33 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="B22" s="2">
-        <v>57.3</v>
+        <v>8.4</v>
       </c>
       <c r="C22" s="2">
-        <v>61.45</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E22" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="B23" s="2">
-        <v>54.9</v>
+        <v>40</v>
       </c>
       <c r="C23" s="2">
-        <v>58.3</v>
+        <v>7.15</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E23" s="2">
         <v>180</v>
@@ -1646,24 +1928,24 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>273</v>
+        <v>94</v>
       </c>
       <c r="B24" s="2">
-        <v>54.35</v>
+        <v>46.5</v>
       </c>
       <c r="C24" s="2">
-        <v>65.525000000000006</v>
+        <v>27.824999999999999</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E24" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>274</v>
+        <v>112</v>
       </c>
       <c r="B25" s="2">
         <v>33.5</v>
@@ -1672,7 +1954,7 @@
         <v>27.824999999999999</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E25" s="2">
         <v>90</v>
@@ -1680,67 +1962,67 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B26" s="2">
-        <v>40</v>
+        <v>63.075000000000003</v>
       </c>
       <c r="C26" s="2">
-        <v>7.15</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E26" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B27" s="2">
-        <v>46.5</v>
+        <v>40</v>
       </c>
       <c r="C27" s="2">
-        <v>27.824999999999999</v>
+        <v>29.824999999999999</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E27" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>277</v>
+        <v>126</v>
       </c>
       <c r="B28" s="2">
-        <v>39.9</v>
+        <v>70.8</v>
       </c>
       <c r="C28" s="2">
-        <v>15.6</v>
+        <v>61.95</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E28" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B29" s="2">
-        <v>21.8</v>
+        <v>70.650000000000006</v>
       </c>
       <c r="C29" s="2">
-        <v>39.1</v>
+        <v>60.15</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E29" s="2">
         <v>0</v>
@@ -1748,50 +2030,50 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="B30" s="2">
-        <v>63.075000000000003</v>
+        <v>66.3</v>
       </c>
       <c r="C30" s="2">
-        <v>38.700000000000003</v>
+        <v>61.95</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E30" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B31" s="2">
-        <v>40</v>
+        <v>65.8</v>
       </c>
       <c r="C31" s="2">
-        <v>29.824999999999999</v>
+        <v>60.15</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E31" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B32" s="2">
-        <v>70.650000000000006</v>
+        <v>46.1</v>
       </c>
       <c r="C32" s="2">
-        <v>60.15</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="E32" s="2">
         <v>0</v>
@@ -1799,33 +2081,33 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="B33" s="2">
-        <v>65.8</v>
+        <v>63.024999999999999</v>
       </c>
       <c r="C33" s="2">
-        <v>60.15</v>
+        <v>39.409999999999997</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="E33" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B34" s="2">
-        <v>70.8</v>
+        <v>63.03</v>
       </c>
       <c r="C34" s="2">
-        <v>61.95</v>
+        <v>37.85</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="E34" s="2">
         <v>0</v>
@@ -1833,121 +2115,121 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>284</v>
+        <v>5</v>
       </c>
       <c r="B35" s="2">
-        <v>66.3</v>
+        <v>72.8</v>
       </c>
       <c r="C35" s="2">
-        <v>61.95</v>
+        <v>38.479999999999997</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="E35" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B36" s="2">
-        <v>46.1</v>
+        <v>68.58</v>
       </c>
       <c r="C36" s="2">
-        <v>38.299999999999997</v>
+        <v>42.92</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E36" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B37" s="2">
-        <v>9.8800000000000008</v>
+        <v>70.09</v>
       </c>
       <c r="C37" s="2">
-        <v>29.49</v>
+        <v>42.94</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E37" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B38" s="2">
-        <v>11.99</v>
+        <v>67.08</v>
       </c>
       <c r="C38" s="2">
-        <v>26.85</v>
+        <v>42.914999999999999</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E38" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B39" s="2">
-        <v>63.024999999999999</v>
+        <v>73.47</v>
       </c>
       <c r="C39" s="2">
-        <v>39.409999999999997</v>
+        <v>41.15</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E39" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B40" s="2">
-        <v>6.3797930000000003</v>
+        <v>72.47</v>
       </c>
       <c r="C40" s="2">
-        <v>54.952869</v>
+        <v>42.63</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E40" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>10</v>
+        <v>239</v>
       </c>
       <c r="B41" s="2">
-        <v>11.6972</v>
+        <v>33.75</v>
       </c>
       <c r="C41" s="2">
-        <v>41.7301</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E41" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1955,16 +2237,16 @@
         <v>11</v>
       </c>
       <c r="B42" s="2">
-        <v>13.6784</v>
+        <v>56.35</v>
       </c>
       <c r="C42" s="2">
-        <v>41.7301</v>
+        <v>7.45</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E42" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1972,16 +2254,16 @@
         <v>12</v>
       </c>
       <c r="B43" s="2">
-        <v>12.713200000000001</v>
+        <v>56.35</v>
       </c>
       <c r="C43" s="2">
-        <v>41.7301</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E43" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1989,98 +2271,98 @@
         <v>13</v>
       </c>
       <c r="B44" s="2">
-        <v>14.643599999999999</v>
+        <v>56.35</v>
       </c>
       <c r="C44" s="2">
-        <v>41.7301</v>
+        <v>6.45</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E44" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2" t="s">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="B45" s="2">
-        <v>17.968399999999999</v>
+        <v>53.8</v>
       </c>
       <c r="C45" s="2">
-        <v>38.834499999999998</v>
+        <v>4.95</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E45" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B46" s="2">
-        <v>20.195207</v>
+        <v>51.5</v>
       </c>
       <c r="C46" s="2">
-        <v>34.527130999999997</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E46" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B47" s="2">
-        <v>8.4700000000000006</v>
+        <v>56.35</v>
       </c>
       <c r="C47" s="2">
-        <v>41.3</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E47" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2" t="s">
-        <v>17</v>
+        <v>241</v>
       </c>
       <c r="B48" s="2">
-        <v>15.6088</v>
+        <v>54.8</v>
       </c>
       <c r="C48" s="2">
-        <v>41.7301</v>
+        <v>4.95</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E48" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B49" s="2">
-        <v>63.063892000000003</v>
+        <v>52.8</v>
       </c>
       <c r="C49" s="2">
-        <v>49.296168999999999</v>
+        <v>4.95</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E49" s="2">
         <v>-90</v>
@@ -2088,118 +2370,118 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B50" s="2">
-        <v>51.07</v>
+        <v>54.35</v>
       </c>
       <c r="C50" s="2">
-        <v>49.5</v>
+        <v>11.66</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E50" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2" t="s">
-        <v>20</v>
+        <v>242</v>
       </c>
       <c r="B51" s="2">
-        <v>47.9</v>
+        <v>55.35</v>
       </c>
       <c r="C51" s="2">
-        <v>52.9</v>
+        <v>11.66</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E51" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2" t="s">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="B52" s="2">
-        <v>44.65</v>
+        <v>28.774999999999999</v>
       </c>
       <c r="C52" s="2">
-        <v>53.9</v>
+        <v>8.35</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E52" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2" t="s">
-        <v>22</v>
+        <v>244</v>
       </c>
       <c r="B53" s="2">
-        <v>38</v>
+        <v>28.774999999999999</v>
       </c>
       <c r="C53" s="2">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E53" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B54" s="2">
-        <v>42.05</v>
+        <v>51.07</v>
       </c>
       <c r="C54" s="2">
-        <v>36.9</v>
+        <v>49.5</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E54" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B55" s="2">
-        <v>40.844892000000002</v>
+        <v>47.9</v>
       </c>
       <c r="C55" s="2">
-        <v>35.156168999999998</v>
+        <v>52.9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E55" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B56" s="2">
-        <v>48.496892000000003</v>
+        <v>44.65</v>
       </c>
       <c r="C56" s="2">
-        <v>37.541168999999996</v>
+        <v>53.9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E56" s="2">
         <v>90</v>
@@ -2207,33 +2489,33 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B57" s="2">
-        <v>40.844892000000002</v>
+        <v>63.063892000000003</v>
       </c>
       <c r="C57" s="2">
-        <v>30.584168999999999</v>
+        <v>49.296168999999999</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E57" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B58" s="2">
-        <v>49.75</v>
+        <v>60.711891999999999</v>
       </c>
       <c r="C58" s="2">
-        <v>37</v>
+        <v>41.491168999999999</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E58" s="2">
         <v>-90</v>
@@ -2241,50 +2523,50 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B59" s="2">
-        <v>49.861891999999997</v>
+        <v>57.141891999999999</v>
       </c>
       <c r="C59" s="2">
-        <v>34.267169000000003</v>
+        <v>50.561169</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E59" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B60" s="2">
-        <v>49.861891999999997</v>
+        <v>60.486891999999997</v>
       </c>
       <c r="C60" s="2">
-        <v>31.219169000000001</v>
+        <v>45.566169000000002</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E60" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B61" s="2">
-        <v>43.511892000000003</v>
+        <v>53.91</v>
       </c>
       <c r="C61" s="2">
-        <v>28.077131000000001</v>
+        <v>54.92</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E61" s="2">
         <v>90</v>
@@ -2292,16 +2574,16 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B62" s="2">
-        <v>45.543892</v>
+        <v>38</v>
       </c>
       <c r="C62" s="2">
-        <v>28.077131000000001</v>
+        <v>37</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E62" s="2">
         <v>90</v>
@@ -2309,101 +2591,101 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B63" s="2">
-        <v>47.25</v>
+        <v>17.809999999999999</v>
       </c>
       <c r="C63" s="2">
-        <v>28.077131000000001</v>
+        <v>43.083799999999997</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E63" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B64" s="2">
-        <v>23.178201000000001</v>
+        <v>15.4948</v>
       </c>
       <c r="C64" s="2">
-        <v>33.856099999999998</v>
+        <v>44.724400000000003</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E64" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B65" s="2">
-        <v>18.5044</v>
+        <v>19.2</v>
       </c>
       <c r="C65" s="2">
-        <v>35.989699999999999</v>
+        <v>44</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E65" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B66" s="2">
-        <v>25.7</v>
+        <v>15.4948</v>
       </c>
       <c r="C66" s="2">
-        <v>41.5</v>
+        <v>47.772399999999998</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E66" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B67" s="2">
-        <v>28.88</v>
+        <v>42.05</v>
       </c>
       <c r="C67" s="2">
-        <v>36.5</v>
+        <v>36.9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E67" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B68" s="2">
-        <v>50.2</v>
+        <v>48.496892000000003</v>
       </c>
       <c r="C68" s="2">
-        <v>15.18</v>
+        <v>37.541168999999996</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E68" s="2">
         <v>90</v>
@@ -2411,50 +2693,50 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2" t="s">
-        <v>38</v>
+        <v>245</v>
       </c>
       <c r="B69" s="2">
-        <v>38.799999999999997</v>
+        <v>40.844892000000002</v>
       </c>
       <c r="C69" s="2">
-        <v>15.6</v>
+        <v>35.156168999999998</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E69" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B70" s="2">
-        <v>49</v>
+        <v>49.75</v>
       </c>
       <c r="C70" s="2">
-        <v>15.475</v>
+        <v>37</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E70" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B71" s="2">
-        <v>37.6</v>
+        <v>17.3124</v>
       </c>
       <c r="C71" s="2">
-        <v>14.975</v>
+        <v>51.573300000000003</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E71" s="2">
         <v>90</v>
@@ -2462,33 +2744,33 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B72" s="2">
-        <v>13.717499999999999</v>
+        <v>40.844892000000002</v>
       </c>
       <c r="C72" s="2">
-        <v>21.42</v>
+        <v>30.584168999999999</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E72" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2" t="s">
-        <v>286</v>
+        <v>38</v>
       </c>
       <c r="B73" s="2">
-        <v>63.03</v>
+        <v>19.598400000000002</v>
       </c>
       <c r="C73" s="2">
-        <v>37.85</v>
+        <v>50.811300000000003</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E73" s="2">
         <v>0</v>
@@ -2496,16 +2778,16 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2" t="s">
-        <v>287</v>
+        <v>39</v>
       </c>
       <c r="B74" s="2">
-        <v>73.47</v>
+        <v>21.859000000000002</v>
       </c>
       <c r="C74" s="2">
-        <v>41.15</v>
+        <v>51.573300000000003</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E74" s="2">
         <v>-90</v>
@@ -2513,271 +2795,271 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B75" s="2">
-        <v>17.809999999999999</v>
+        <v>49.861891999999997</v>
       </c>
       <c r="C75" s="2">
-        <v>43.083799999999997</v>
+        <v>34.267169000000003</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E75" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B76" s="2">
-        <v>19.2</v>
+        <v>21.880400000000002</v>
       </c>
       <c r="C76" s="2">
-        <v>44</v>
+        <v>54.599699999999999</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E76" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2" t="s">
-        <v>44</v>
+        <v>271</v>
       </c>
       <c r="B77" s="2">
-        <v>15.4948</v>
+        <v>49.861891999999997</v>
       </c>
       <c r="C77" s="2">
-        <v>44.724400000000003</v>
+        <v>31.219169000000001</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E77" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2" t="s">
-        <v>45</v>
+        <v>272</v>
       </c>
       <c r="B78" s="2">
-        <v>15.4948</v>
+        <v>21.9</v>
       </c>
       <c r="C78" s="2">
-        <v>47.772399999999998</v>
+        <v>56.48</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E78" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2" t="s">
-        <v>46</v>
+        <v>285</v>
       </c>
       <c r="B79" s="2">
-        <v>17.3124</v>
+        <v>24.6784</v>
       </c>
       <c r="C79" s="2">
-        <v>51.573300000000003</v>
+        <v>42.554931000000003</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E79" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2" t="s">
-        <v>47</v>
+        <v>286</v>
       </c>
       <c r="B80" s="2">
-        <v>19.598400000000002</v>
+        <v>44.3</v>
       </c>
       <c r="C80" s="2">
-        <v>50.811300000000003</v>
+        <v>28.4</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E80" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2" t="s">
-        <v>48</v>
+        <v>287</v>
       </c>
       <c r="B81" s="2">
-        <v>21.859000000000002</v>
+        <v>45.543892</v>
       </c>
       <c r="C81" s="2">
-        <v>51.573300000000003</v>
+        <v>28.077131000000001</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E81" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2" t="s">
-        <v>49</v>
+        <v>288</v>
       </c>
       <c r="B82" s="2">
-        <v>21.880400000000002</v>
+        <v>26.202400000000001</v>
       </c>
       <c r="C82" s="2">
-        <v>54.599699999999999</v>
+        <v>45.527130999999997</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E82" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2" t="s">
-        <v>50</v>
+        <v>289</v>
       </c>
       <c r="B83" s="2">
-        <v>21.9</v>
+        <v>26.2</v>
       </c>
       <c r="C83" s="2">
-        <v>56.48</v>
+        <v>43.62</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E83" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2" t="s">
-        <v>51</v>
+        <v>290</v>
       </c>
       <c r="B84" s="2">
-        <v>24.6784</v>
+        <v>47.25</v>
       </c>
       <c r="C84" s="2">
-        <v>42.554931000000003</v>
+        <v>28.077131000000001</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E84" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2" t="s">
-        <v>52</v>
+        <v>291</v>
       </c>
       <c r="B85" s="2">
-        <v>26.202400000000001</v>
+        <v>38.174599999999998</v>
       </c>
       <c r="C85" s="2">
-        <v>45.527130999999997</v>
+        <v>50.7044</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E85" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2" t="s">
-        <v>53</v>
+        <v>292</v>
       </c>
       <c r="B86" s="2">
-        <v>26.2</v>
+        <v>56.75</v>
       </c>
       <c r="C86" s="2">
-        <v>43.62</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E86" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B87" s="2">
-        <v>38.174599999999998</v>
+        <v>60</v>
       </c>
       <c r="C87" s="2">
-        <v>50.7044</v>
+        <v>61.8</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E87" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B88" s="2">
-        <v>39.695207000000003</v>
+        <v>53.35</v>
       </c>
       <c r="C88" s="2">
-        <v>50.727131</v>
+        <v>65.81</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E88" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B89" s="2">
-        <v>35.954199000000003</v>
+        <v>39.695207000000003</v>
       </c>
       <c r="C89" s="2">
-        <v>40.634799999999998</v>
+        <v>50.727131</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E89" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B90" s="2">
-        <v>34.430199000000002</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="C90" s="2">
-        <v>40.634799999999998</v>
+        <v>29.49</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E90" s="2">
         <v>-90</v>
@@ -2785,135 +3067,135 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B91" s="2">
-        <v>34.836599</v>
+        <v>11.99</v>
       </c>
       <c r="C91" s="2">
-        <v>50.693199999999997</v>
+        <v>26.85</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E91" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B92" s="2">
-        <v>29.75</v>
+        <v>35.954199000000003</v>
       </c>
       <c r="C92" s="2">
-        <v>46.7</v>
+        <v>40.634799999999998</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E92" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B93" s="2">
-        <v>37</v>
+        <v>57.55</v>
       </c>
       <c r="C93" s="2">
-        <v>42.1</v>
+        <v>62.65</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E93" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B94" s="2">
-        <v>43.75</v>
+        <v>34.430199000000002</v>
       </c>
       <c r="C94" s="2">
-        <v>20.75</v>
+        <v>40.634799999999998</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E94" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B95" s="2">
-        <v>30.85</v>
+        <v>6.3797930000000003</v>
       </c>
       <c r="C95" s="2">
-        <v>44.087200000000003</v>
+        <v>54.952869</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E95" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B96" s="2">
-        <v>47.25</v>
+        <v>34.836599</v>
       </c>
       <c r="C96" s="2">
-        <v>41</v>
+        <v>50.693199999999997</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E96" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B97" s="2">
-        <v>39.995207000000001</v>
+        <v>29.75</v>
       </c>
       <c r="C97" s="2">
-        <v>46.427131000000003</v>
+        <v>46.7</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E97" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B98" s="2">
-        <v>45.769199999999998</v>
+        <v>42.55</v>
       </c>
       <c r="C98" s="2">
-        <v>40.987200000000001</v>
+        <v>19.7</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E98" s="2">
         <v>-90</v>
@@ -2921,152 +3203,152 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B99" s="2">
-        <v>28.9</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="C99" s="2">
-        <v>43.9</v>
+        <v>24.07</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E99" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B100" s="2">
-        <v>38.495207000000001</v>
+        <v>44.63</v>
       </c>
       <c r="C100" s="2">
-        <v>46.452131000000001</v>
+        <v>19.79</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E100" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="B101" s="2">
-        <v>51.2</v>
+        <v>38.950000000000003</v>
       </c>
       <c r="C101" s="2">
-        <v>40.25</v>
+        <v>23.5</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E101" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B102" s="2">
-        <v>53.5</v>
+        <v>11.6972</v>
       </c>
       <c r="C102" s="2">
-        <v>40.25</v>
+        <v>41.7301</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E102" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B103" s="2">
-        <v>25.725000000000001</v>
+        <v>37</v>
       </c>
       <c r="C103" s="2">
-        <v>23</v>
+        <v>42.1</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E103" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B104" s="2">
-        <v>72.47</v>
+        <v>56.274999999999999</v>
       </c>
       <c r="C104" s="2">
-        <v>42.63</v>
+        <v>59.2</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E104" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B105" s="2">
-        <v>53.225000000000001</v>
+        <v>13.6784</v>
       </c>
       <c r="C105" s="2">
-        <v>20.725000000000001</v>
+        <v>41.7301</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E105" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B106" s="2">
-        <v>35.299999999999997</v>
+        <v>48.36</v>
       </c>
       <c r="C106" s="2">
-        <v>23</v>
+        <v>58.575000000000003</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E106" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B107" s="2">
-        <v>49.2</v>
+        <v>46.9</v>
       </c>
       <c r="C107" s="2">
-        <v>27.3</v>
+        <v>58.575000000000003</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E107" s="2">
         <v>-90</v>
@@ -3074,50 +3356,50 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B108" s="2">
-        <v>72.8</v>
+        <v>30.85</v>
       </c>
       <c r="C108" s="2">
-        <v>38.479999999999997</v>
+        <v>44.087200000000003</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E108" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2" t="s">
-        <v>76</v>
+        <v>293</v>
       </c>
       <c r="B109" s="2">
-        <v>68.58</v>
+        <v>47.25</v>
       </c>
       <c r="C109" s="2">
-        <v>42.92</v>
+        <v>41</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E109" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B110" s="2">
-        <v>70.09</v>
+        <v>39.995207000000001</v>
       </c>
       <c r="C110" s="2">
-        <v>42.94</v>
+        <v>46.427131000000003</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E110" s="2">
         <v>90</v>
@@ -3125,118 +3407,118 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B111" s="2">
-        <v>67.08</v>
+        <v>44.55</v>
       </c>
       <c r="C111" s="2">
-        <v>42.914999999999999</v>
+        <v>57.75</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E111" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B112" s="2">
-        <v>23.725000000000001</v>
+        <v>50.6</v>
       </c>
       <c r="C112" s="2">
-        <v>58.95</v>
+        <v>61.58</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E112" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2" t="s">
-        <v>80</v>
+        <v>294</v>
       </c>
       <c r="B113" s="2">
-        <v>41</v>
+        <v>45.769199999999998</v>
       </c>
       <c r="C113" s="2">
-        <v>28.024999999999999</v>
+        <v>40.987200000000001</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E113" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2" t="s">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="B114" s="2">
-        <v>60.711891999999999</v>
+        <v>38.495207000000001</v>
       </c>
       <c r="C114" s="2">
-        <v>41.491168999999999</v>
+        <v>46.452131000000001</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E114" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B115" s="2">
-        <v>57.141891999999999</v>
+        <v>49.1</v>
       </c>
       <c r="C115" s="2">
-        <v>50.561169</v>
+        <v>61.58</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E115" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2" t="s">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="B116" s="2">
-        <v>60.486891999999997</v>
+        <v>12.713200000000001</v>
       </c>
       <c r="C116" s="2">
-        <v>45.566169000000002</v>
+        <v>41.7301</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E116" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2" t="s">
-        <v>84</v>
+        <v>297</v>
       </c>
       <c r="B117" s="2">
-        <v>53.91</v>
+        <v>14.643599999999999</v>
       </c>
       <c r="C117" s="2">
-        <v>54.92</v>
+        <v>41.7301</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E117" s="2">
         <v>90</v>
@@ -3244,322 +3526,322 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B118" s="2">
-        <v>30.675000000000001</v>
+        <v>49</v>
       </c>
       <c r="C118" s="2">
-        <v>53.65</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E118" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B119" s="2">
-        <v>30.65</v>
+        <v>47.6</v>
       </c>
       <c r="C119" s="2">
-        <v>56</v>
+        <v>61.58</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E119" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B120" s="2">
-        <v>30.65</v>
+        <v>51.2</v>
       </c>
       <c r="C120" s="2">
-        <v>58.3</v>
+        <v>40.25</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E120" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B121" s="2">
-        <v>57.55</v>
+        <v>17.968399999999999</v>
       </c>
       <c r="C121" s="2">
-        <v>62.65</v>
+        <v>38.834499999999998</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E121" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B122" s="2">
-        <v>56.75</v>
+        <v>45.25</v>
       </c>
       <c r="C122" s="2">
-        <v>65.900000000000006</v>
+        <v>62.4</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E122" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B123" s="2">
-        <v>60</v>
+        <v>13.717499999999999</v>
       </c>
       <c r="C123" s="2">
-        <v>61.8</v>
+        <v>21.42</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E123" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B124" s="2">
-        <v>53.35</v>
+        <v>18.420000000000002</v>
       </c>
       <c r="C124" s="2">
-        <v>65.81</v>
+        <v>35.1</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E124" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B125" s="2">
-        <v>56.274999999999999</v>
+        <v>53.5</v>
       </c>
       <c r="C125" s="2">
-        <v>59.2</v>
+        <v>40.25</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E125" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B126" s="2">
-        <v>48.36</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="C126" s="2">
-        <v>58.575000000000003</v>
+        <v>41.3</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E126" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B127" s="2">
-        <v>46.9</v>
+        <v>15.6088</v>
       </c>
       <c r="C127" s="2">
-        <v>58.575000000000003</v>
+        <v>41.7301</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E127" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B128" s="2">
-        <v>44.55</v>
+        <v>28.2</v>
       </c>
       <c r="C128" s="2">
-        <v>57.75</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E128" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2" t="s">
-        <v>96</v>
+        <v>383</v>
       </c>
       <c r="B129" s="2">
-        <v>50.6</v>
+        <v>22.2</v>
       </c>
       <c r="C129" s="2">
-        <v>61.58</v>
+        <v>33.15</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E129" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2" t="s">
-        <v>97</v>
+        <v>246</v>
       </c>
       <c r="B130" s="2">
-        <v>41.35</v>
+        <v>71.02</v>
       </c>
       <c r="C130" s="2">
-        <v>57.75</v>
+        <v>22.3</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E130" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
-        <v>98</v>
+        <v>248</v>
       </c>
       <c r="B131" s="2">
-        <v>49.1</v>
+        <v>20.67</v>
       </c>
       <c r="C131" s="2">
-        <v>61.58</v>
+        <v>23.05</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E131" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2" t="s">
-        <v>99</v>
+        <v>249</v>
       </c>
       <c r="B132" s="2">
-        <v>38.15</v>
+        <v>55.63</v>
       </c>
       <c r="C132" s="2">
-        <v>57.75</v>
+        <v>21.15</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E132" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2" t="s">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="B133" s="2">
-        <v>47.6</v>
+        <v>69.47</v>
       </c>
       <c r="C133" s="2">
-        <v>61.58</v>
+        <v>23.3</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E133" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2" t="s">
-        <v>101</v>
+        <v>251</v>
       </c>
       <c r="B134" s="2">
-        <v>45.25</v>
+        <v>25.524999999999999</v>
       </c>
       <c r="C134" s="2">
-        <v>62.4</v>
+        <v>69.290000000000006</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E134" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2" t="s">
-        <v>102</v>
+        <v>252</v>
       </c>
       <c r="B135" s="2">
-        <v>42.05</v>
+        <v>30.358332000000001</v>
       </c>
       <c r="C135" s="2">
-        <v>62.4</v>
+        <v>69.290000000000006</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E135" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2" t="s">
-        <v>103</v>
+        <v>253</v>
       </c>
       <c r="B136" s="2">
-        <v>32.774999999999999</v>
+        <v>27.941666000000001</v>
       </c>
       <c r="C136" s="2">
         <v>69.290000000000006</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E136" s="2">
         <v>90</v>
@@ -3567,33 +3849,33 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2" t="s">
-        <v>104</v>
+        <v>254</v>
       </c>
       <c r="B137" s="2">
-        <v>25.524999999999999</v>
+        <v>59.7</v>
       </c>
       <c r="C137" s="2">
-        <v>69.290000000000006</v>
+        <v>64.5</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E137" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2" t="s">
-        <v>105</v>
+        <v>256</v>
       </c>
       <c r="B138" s="2">
-        <v>27.941666000000001</v>
+        <v>53.75</v>
       </c>
       <c r="C138" s="2">
-        <v>69.290000000000006</v>
+        <v>68</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E138" s="2">
         <v>90</v>
@@ -3601,33 +3883,33 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2" t="s">
-        <v>106</v>
+        <v>257</v>
       </c>
       <c r="B139" s="2">
-        <v>49.2</v>
+        <v>32.774999999999999</v>
       </c>
       <c r="C139" s="2">
-        <v>65.55</v>
+        <v>69.290000000000006</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E139" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B140" s="2">
-        <v>30.358332000000001</v>
+        <v>42.845207000000002</v>
       </c>
       <c r="C140" s="2">
-        <v>69.290000000000006</v>
+        <v>47.827131000000001</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E140" s="2">
         <v>90</v>
@@ -3635,16 +3917,16 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2" t="s">
-        <v>108</v>
+        <v>259</v>
       </c>
       <c r="B141" s="2">
-        <v>44</v>
+        <v>49.2</v>
       </c>
       <c r="C141" s="2">
-        <v>65.95</v>
+        <v>65.55</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E141" s="2">
         <v>180</v>
@@ -3652,33 +3934,33 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="B142" s="2">
-        <v>42.845207000000002</v>
+        <v>44</v>
       </c>
       <c r="C142" s="2">
-        <v>47.827131000000001</v>
+        <v>65.95</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E142" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B143" s="2">
-        <v>53.75</v>
+        <v>39.25</v>
       </c>
       <c r="C143" s="2">
-        <v>68</v>
+        <v>62.3</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E143" s="2">
         <v>90</v>
@@ -3686,16 +3968,16 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B144" s="2">
-        <v>39.25</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="C144" s="2">
-        <v>62.3</v>
+        <v>20.984999999999999</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E144" s="2">
         <v>90</v>
@@ -3703,24 +3985,24 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B145" s="2">
-        <v>59.7</v>
+        <v>77</v>
       </c>
       <c r="C145" s="2">
-        <v>64.5</v>
+        <v>15.734999999999999</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E145" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="B146" s="2">
         <v>26.387</v>
@@ -3729,7 +4011,7 @@
         <v>58.475000000000001</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E146" s="2">
         <v>0</v>
@@ -3737,7 +4019,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="B147" s="2">
         <v>68.3</v>
@@ -3746,7 +4028,7 @@
         <v>65.150001000000003</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E147" s="2">
         <v>180</v>
@@ -3754,126 +4036,126 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="B148" s="2">
-        <v>8.99</v>
+        <v>47.1</v>
       </c>
       <c r="C148" s="2">
-        <v>67.73</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E148" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="B149" s="2">
-        <v>47.1</v>
+        <v>8.99</v>
       </c>
       <c r="C149" s="2">
-        <v>67.900000000000006</v>
+        <v>67.73</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E149" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B150" s="2">
-        <v>54.052892</v>
+        <v>69.09</v>
       </c>
       <c r="C150" s="2">
-        <v>32.743169000000002</v>
+        <v>32.78</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E150" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="B151" s="2">
-        <v>41.195207000000003</v>
+        <v>27.0745</v>
       </c>
       <c r="C151" s="2">
-        <v>41.327131000000001</v>
+        <v>13.75</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E151" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="B152" s="2">
-        <v>69.09</v>
+        <v>54.052892</v>
       </c>
       <c r="C152" s="2">
-        <v>32.78</v>
+        <v>32.743169000000002</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E152" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="B153" s="2">
-        <v>50.191099999999999</v>
+        <v>41.195207000000003</v>
       </c>
       <c r="C153" s="2">
-        <v>45.563400000000001</v>
+        <v>41.327131000000001</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E153" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B154" s="2">
-        <v>23.795207000000001</v>
+        <v>50.191099999999999</v>
       </c>
       <c r="C154" s="2">
-        <v>49.927131000000003</v>
+        <v>45.563400000000001</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E154" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="B155" s="2">
         <v>60.02</v>
@@ -3882,7 +4164,7 @@
         <v>55.987499999999997</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E155" s="2">
         <v>-90</v>
@@ -3890,7 +4172,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2" t="s">
-        <v>123</v>
+        <v>298</v>
       </c>
       <c r="B156" s="2">
         <v>56.342500000000001</v>
@@ -3899,7 +4181,7 @@
         <v>54.45</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E156" s="2">
         <v>180</v>
@@ -3907,33 +4189,33 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="B157" s="2">
-        <v>23.127400999999999</v>
+        <v>19.087499999999999</v>
       </c>
       <c r="C157" s="2">
-        <v>37.509900000000002</v>
+        <v>58.55</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E157" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="B158" s="2">
-        <v>10.817500000000001</v>
+        <v>23.795207000000001</v>
       </c>
       <c r="C158" s="2">
-        <v>22.650001</v>
+        <v>49.927131000000003</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E158" s="2">
         <v>-90</v>
@@ -3941,101 +4223,101 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B159" s="2">
-        <v>19.087499999999999</v>
+        <v>10.817500000000001</v>
       </c>
       <c r="C159" s="2">
-        <v>58.55</v>
+        <v>22.650001</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E159" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2" t="s">
-        <v>127</v>
+        <v>299</v>
       </c>
       <c r="B160" s="2">
-        <v>6.34</v>
+        <v>74.150000000000006</v>
       </c>
       <c r="C160" s="2">
-        <v>44.1</v>
+        <v>18.46</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E160" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="B161" s="2">
-        <v>17.995207000000001</v>
+        <v>52.15</v>
       </c>
       <c r="C161" s="2">
-        <v>40.827131000000001</v>
+        <v>52.255000000000003</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E161" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="B162" s="2">
-        <v>17.996400000000001</v>
+        <v>50.19</v>
       </c>
       <c r="C162" s="2">
-        <v>39.827131000000001</v>
+        <v>52.262500000000003</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E162" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2" t="s">
-        <v>130</v>
+        <v>261</v>
       </c>
       <c r="B163" s="2">
-        <v>13.79</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="C163" s="2">
-        <v>29.14</v>
+        <v>31.4</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E163" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2" t="s">
-        <v>131</v>
+        <v>262</v>
       </c>
       <c r="B164" s="2">
-        <v>30.6</v>
+        <v>31.45</v>
       </c>
       <c r="C164" s="2">
-        <v>30.3</v>
+        <v>31.4</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E164" s="2">
         <v>90</v>
@@ -4043,118 +4325,118 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="B165" s="2">
-        <v>31.6</v>
+        <v>32.826960999999997</v>
       </c>
       <c r="C165" s="2">
-        <v>28.8</v>
+        <v>33.85</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E165" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="B166" s="2">
-        <v>19.482500000000002</v>
+        <v>31.3</v>
       </c>
       <c r="C166" s="2">
-        <v>61.09</v>
+        <v>33.819400000000002</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E166" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="B167" s="2">
-        <v>24.145206999999999</v>
+        <v>55.72</v>
       </c>
       <c r="C167" s="2">
-        <v>30.402131000000001</v>
+        <v>15.32</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E167" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2" t="s">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="B168" s="2">
-        <v>68.7</v>
+        <v>26.65</v>
       </c>
       <c r="C168" s="2">
-        <v>19.912500000000001</v>
+        <v>55.15</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E168" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="B169" s="2">
-        <v>30.6</v>
+        <v>26.637499999999999</v>
       </c>
       <c r="C169" s="2">
-        <v>33.325000000000003</v>
+        <v>53.225000000000001</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E169" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="B170" s="2">
-        <v>32.125</v>
+        <v>46.7</v>
       </c>
       <c r="C170" s="2">
-        <v>30.774999999999999</v>
+        <v>45.3</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E170" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="B171" s="2">
-        <v>46.709000000000003</v>
+        <v>42.15</v>
       </c>
       <c r="C171" s="2">
-        <v>48.342199999999998</v>
+        <v>52.398212999999998</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E171" s="2">
         <v>180</v>
@@ -4162,118 +4444,118 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="B172" s="2">
-        <v>46.709000000000003</v>
+        <v>42.15</v>
       </c>
       <c r="C172" s="2">
-        <v>46.818199999999997</v>
+        <v>54.35</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E172" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B173" s="2">
-        <v>49.759300000000003</v>
+        <v>32.6</v>
       </c>
       <c r="C173" s="2">
-        <v>48.078000000000003</v>
+        <v>39.6</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E173" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B174" s="2">
-        <v>36.780892000000001</v>
+        <v>29.4</v>
       </c>
       <c r="C174" s="2">
-        <v>37.328169000000003</v>
+        <v>51.35</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E174" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="B175" s="2">
-        <v>40.844892000000002</v>
+        <v>54.13</v>
       </c>
       <c r="C175" s="2">
-        <v>32.108168999999997</v>
+        <v>15.335000000000001</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E175" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="B176" s="2">
-        <v>40.844892000000002</v>
+        <v>35.020000000000003</v>
       </c>
       <c r="C176" s="2">
-        <v>33.632168999999998</v>
+        <v>16.8825</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E176" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2" t="s">
-        <v>144</v>
+        <v>301</v>
       </c>
       <c r="B177" s="2">
-        <v>18.5044</v>
+        <v>46.596891999999997</v>
       </c>
       <c r="C177" s="2">
-        <v>37.5137</v>
+        <v>35.826169</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E177" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="B178" s="2">
-        <v>27</v>
+        <v>44.596891999999997</v>
       </c>
       <c r="C178" s="2">
-        <v>41.125</v>
+        <v>35.821168999999998</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E178" s="2">
         <v>-90</v>
@@ -4281,101 +4563,101 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="B179" s="2">
-        <v>27.711400000000001</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="C179" s="2">
-        <v>37.863199999999999</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E179" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="B180" s="2">
-        <v>32.11</v>
+        <v>71.400000000000006</v>
       </c>
       <c r="C180" s="2">
-        <v>9.1</v>
+        <v>47.5</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E180" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="B181" s="2">
-        <v>43.1</v>
+        <v>52.43</v>
       </c>
       <c r="C181" s="2">
-        <v>15.2</v>
+        <v>26.3</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E181" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="B182" s="2">
-        <v>50.3</v>
+        <v>52.43</v>
       </c>
       <c r="C182" s="2">
-        <v>10.65</v>
+        <v>28.31</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E182" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2" t="s">
-        <v>150</v>
+        <v>302</v>
       </c>
       <c r="B183" s="2">
-        <v>30.6</v>
+        <v>34.35</v>
       </c>
       <c r="C183" s="2">
-        <v>9.1</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E183" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="B184" s="2">
-        <v>31.8</v>
+        <v>49.27</v>
       </c>
       <c r="C184" s="2">
-        <v>15.525</v>
+        <v>20.3</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E184" s="2">
         <v>-90</v>
@@ -4383,16 +4665,16 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="B185" s="2">
-        <v>15.4948</v>
+        <v>72.375</v>
       </c>
       <c r="C185" s="2">
-        <v>49.296399999999998</v>
+        <v>37.26</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E185" s="2">
         <v>0</v>
@@ -4400,50 +4682,50 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2" t="s">
-        <v>153</v>
+        <v>303</v>
       </c>
       <c r="B186" s="2">
-        <v>15.4948</v>
+        <v>64.8</v>
       </c>
       <c r="C186" s="2">
-        <v>46.248399999999997</v>
+        <v>42.12</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E186" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2" t="s">
-        <v>154</v>
+        <v>304</v>
       </c>
       <c r="B187" s="2">
-        <v>18.836400000000001</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="C187" s="2">
-        <v>53.084099999999999</v>
+        <v>45.3</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E187" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="B188" s="2">
-        <v>19.398399999999999</v>
+        <v>43.8</v>
       </c>
       <c r="C188" s="2">
-        <v>55.557899999999997</v>
+        <v>4.95</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E188" s="2">
         <v>180</v>
@@ -4451,101 +4733,101 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="B189" s="2">
-        <v>20.359000000000002</v>
+        <v>46.45</v>
       </c>
       <c r="C189" s="2">
-        <v>53.084099999999999</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E189" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="B190" s="2">
-        <v>23.154399999999999</v>
+        <v>44.1</v>
       </c>
       <c r="C190" s="2">
-        <v>46.213900000000002</v>
+        <v>8.6</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E190" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="B191" s="2">
-        <v>23.154399999999999</v>
+        <v>46.45</v>
       </c>
       <c r="C191" s="2">
-        <v>43.203499999999998</v>
+        <v>8.15</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E191" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="B192" s="2">
-        <v>24.6784</v>
+        <v>36.049999999999997</v>
       </c>
       <c r="C192" s="2">
-        <v>45.552131000000003</v>
+        <v>10.45</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E192" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="B193" s="2">
-        <v>31.788599000000001</v>
+        <v>40.549999999999997</v>
       </c>
       <c r="C193" s="2">
-        <v>50.693199999999997</v>
+        <v>11.5</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E193" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="B194" s="2">
-        <v>36.360599000000001</v>
+        <v>39.549999999999997</v>
       </c>
       <c r="C194" s="2">
-        <v>50.693199999999997</v>
+        <v>11.5</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E194" s="2">
         <v>90</v>
@@ -4553,237 +4835,237 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="B195" s="2">
-        <v>60.136892000000003</v>
+        <v>35.9</v>
       </c>
       <c r="C195" s="2">
-        <v>51.691169000000002</v>
+        <v>13.8</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E195" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="B196" s="2">
-        <v>52.439329000000001</v>
+        <v>33.450000000000003</v>
       </c>
       <c r="C196" s="2">
-        <v>53.53</v>
+        <v>6.3</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E196" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2" t="s">
-        <v>164</v>
+        <v>263</v>
       </c>
       <c r="B197" s="2">
-        <v>50.479329</v>
+        <v>30.54</v>
       </c>
       <c r="C197" s="2">
-        <v>53.537500000000001</v>
+        <v>3.35</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E197" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="B198" s="2">
-        <v>31.91</v>
+        <v>30.95</v>
       </c>
       <c r="C198" s="2">
-        <v>66.950468999999998</v>
+        <v>8.25</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E198" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="B199" s="2">
-        <v>54.664999999999999</v>
+        <v>53.05</v>
       </c>
       <c r="C199" s="2">
-        <v>50.51</v>
+        <v>12.225</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E199" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2" t="s">
-        <v>167</v>
+        <v>305</v>
       </c>
       <c r="B200" s="2">
-        <v>56.136892000000003</v>
+        <v>51.5</v>
       </c>
       <c r="C200" s="2">
-        <v>41.491168999999999</v>
+        <v>12.25</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E200" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="B201" s="2">
-        <v>57.661892000000002</v>
+        <v>25.237500000000001</v>
       </c>
       <c r="C201" s="2">
-        <v>41.491168999999999</v>
+        <v>6.25</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E201" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="B202" s="2">
-        <v>59.186892</v>
+        <v>24.6</v>
       </c>
       <c r="C202" s="2">
-        <v>41.491168999999999</v>
+        <v>3.7</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E202" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="B203" s="2">
-        <v>60.486891999999997</v>
+        <v>22.831499999999998</v>
       </c>
       <c r="C203" s="2">
-        <v>44.041168999999996</v>
+        <v>8.5163419999999999</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E203" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="B204" s="2">
-        <v>60.486891999999997</v>
+        <v>56.6</v>
       </c>
       <c r="C204" s="2">
-        <v>48.616168999999999</v>
+        <v>12.2</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E204" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="B205" s="2">
-        <v>60.486891999999997</v>
+        <v>12.4</v>
       </c>
       <c r="C205" s="2">
-        <v>47.091169000000001</v>
+        <v>16.074999999999999</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E205" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2" t="s">
-        <v>173</v>
+        <v>306</v>
       </c>
       <c r="B206" s="2">
-        <v>56.73</v>
+        <v>10.8</v>
       </c>
       <c r="C206" s="2">
-        <v>56.97</v>
+        <v>15.3</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E206" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2" t="s">
-        <v>174</v>
+        <v>307</v>
       </c>
       <c r="B207" s="2">
-        <v>42.15</v>
+        <v>32.125</v>
       </c>
       <c r="C207" s="2">
-        <v>52.398212999999998</v>
+        <v>13.8</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E207" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2" t="s">
-        <v>175</v>
+        <v>308</v>
       </c>
       <c r="B208" s="2">
-        <v>42.15</v>
+        <v>46.709000000000003</v>
       </c>
       <c r="C208" s="2">
-        <v>54.35</v>
+        <v>48.342199999999998</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E208" s="2">
         <v>180</v>
@@ -4791,101 +5073,101 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2" t="s">
-        <v>176</v>
+        <v>309</v>
       </c>
       <c r="B209" s="2">
-        <v>46.596891999999997</v>
+        <v>46.709000000000003</v>
       </c>
       <c r="C209" s="2">
-        <v>35.826169</v>
+        <v>46.818199999999997</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E209" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2" t="s">
-        <v>177</v>
+        <v>310</v>
       </c>
       <c r="B210" s="2">
-        <v>44.596891999999997</v>
+        <v>49.759300000000003</v>
       </c>
       <c r="C210" s="2">
-        <v>35.821168999999998</v>
+        <v>48.078000000000003</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E210" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2" t="s">
-        <v>178</v>
+        <v>311</v>
       </c>
       <c r="B211" s="2">
-        <v>52.43</v>
+        <v>29.46</v>
       </c>
       <c r="C211" s="2">
-        <v>26.3</v>
+        <v>66.974999999999994</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E211" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2" t="s">
-        <v>179</v>
+        <v>312</v>
       </c>
       <c r="B212" s="2">
-        <v>52.43</v>
+        <v>60.136892000000003</v>
       </c>
       <c r="C212" s="2">
-        <v>28.31</v>
+        <v>51.691169000000002</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E212" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2" t="s">
-        <v>180</v>
+        <v>313</v>
       </c>
       <c r="B213" s="2">
-        <v>46.7</v>
+        <v>56.136892000000003</v>
       </c>
       <c r="C213" s="2">
-        <v>45.3</v>
+        <v>41.491168999999999</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E213" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2" t="s">
-        <v>181</v>
+        <v>314</v>
       </c>
       <c r="B214" s="2">
-        <v>26.65</v>
+        <v>54.664999999999999</v>
       </c>
       <c r="C214" s="2">
-        <v>55.15</v>
+        <v>50.51</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E214" s="2">
         <v>180</v>
@@ -4893,203 +5175,203 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="B215" s="2">
-        <v>26.637499999999999</v>
+        <v>57.661892000000002</v>
       </c>
       <c r="C215" s="2">
-        <v>53.225000000000001</v>
+        <v>41.491168999999999</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E215" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2" t="s">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="B216" s="2">
-        <v>29.4</v>
+        <v>59.186892</v>
       </c>
       <c r="C216" s="2">
-        <v>51.35</v>
+        <v>41.491168999999999</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E216" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2" t="s">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="B217" s="2">
-        <v>29.4</v>
+        <v>60.486891999999997</v>
       </c>
       <c r="C217" s="2">
-        <v>49.825000000000003</v>
+        <v>44.041168999999996</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E217" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="B218" s="2">
-        <v>33.4</v>
+        <v>60.486891999999997</v>
       </c>
       <c r="C218" s="2">
-        <v>50.7</v>
+        <v>48.616168999999999</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E218" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="B219" s="2">
-        <v>35.200000000000003</v>
+        <v>60.486891999999997</v>
       </c>
       <c r="C219" s="2">
-        <v>37.299999999999997</v>
+        <v>47.091169000000001</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E219" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="B220" s="2">
-        <v>71.400000000000006</v>
+        <v>36.780892000000001</v>
       </c>
       <c r="C220" s="2">
-        <v>47.5</v>
+        <v>37.328169000000003</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E220" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="B221" s="2">
-        <v>32.200000000000003</v>
+        <v>15.4948</v>
       </c>
       <c r="C221" s="2">
-        <v>33.799999999999997</v>
+        <v>49.296399999999998</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E221" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="B222" s="2">
-        <v>30.2</v>
+        <v>15.4948</v>
       </c>
       <c r="C222" s="2">
-        <v>15.475</v>
+        <v>46.248399999999997</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E222" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2" t="s">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="B223" s="2">
-        <v>32.6</v>
+        <v>41.15</v>
       </c>
       <c r="C223" s="2">
-        <v>39.6</v>
+        <v>26.574999999999999</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E223" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2" t="s">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="B224" s="2">
-        <v>30.2</v>
+        <v>42.7</v>
       </c>
       <c r="C224" s="2">
-        <v>12.4</v>
+        <v>26.574999999999999</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E224" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="2" t="s">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="B225" s="2">
-        <v>28.7</v>
+        <v>40.844892000000002</v>
       </c>
       <c r="C225" s="2">
-        <v>12.4</v>
+        <v>32.108168999999997</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E225" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="2" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="B226" s="2">
-        <v>60.2</v>
+        <v>40.844892000000002</v>
       </c>
       <c r="C226" s="2">
-        <v>60.3</v>
+        <v>33.632168999999998</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E226" s="2">
         <v>0</v>
@@ -5097,33 +5379,33 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="2" t="s">
-        <v>194</v>
+        <v>315</v>
       </c>
       <c r="B227" s="2">
-        <v>69.900000000000006</v>
+        <v>25.475000000000001</v>
       </c>
       <c r="C227" s="2">
-        <v>45.3</v>
+        <v>30.95</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E227" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="B228" s="2">
-        <v>72.375</v>
+        <v>25.475000000000001</v>
       </c>
       <c r="C228" s="2">
-        <v>37.26</v>
+        <v>32.5</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E228" s="2">
         <v>0</v>
@@ -5131,118 +5413,118 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="2" t="s">
-        <v>196</v>
+        <v>316</v>
       </c>
       <c r="B229" s="2">
-        <v>64.8</v>
+        <v>18.836400000000001</v>
       </c>
       <c r="C229" s="2">
-        <v>42.12</v>
+        <v>53.084099999999999</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E229" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="2" t="s">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="B230" s="2">
-        <v>55.5</v>
+        <v>19.398399999999999</v>
       </c>
       <c r="C230" s="2">
-        <v>66.349999999999994</v>
+        <v>55.557899999999997</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E230" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="2" t="s">
-        <v>198</v>
+        <v>317</v>
       </c>
       <c r="B231" s="2">
-        <v>29.46</v>
+        <v>20.359000000000002</v>
       </c>
       <c r="C231" s="2">
-        <v>66.974999999999994</v>
+        <v>53.084099999999999</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E231" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="2" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="B232" s="2">
-        <v>54.4</v>
+        <v>19.482500000000002</v>
       </c>
       <c r="C232" s="2">
-        <v>63.2</v>
+        <v>61.09</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E232" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="2" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="B233" s="2">
-        <v>60.25</v>
+        <v>23.154399999999999</v>
       </c>
       <c r="C233" s="2">
-        <v>63.3</v>
+        <v>46.213900000000002</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E233" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="2" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="B234" s="2">
-        <v>54.3</v>
+        <v>23.154399999999999</v>
       </c>
       <c r="C234" s="2">
-        <v>65.790000000000006</v>
+        <v>43.203499999999998</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E234" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="2" t="s">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="B235" s="2">
-        <v>52.15</v>
+        <v>24.6784</v>
       </c>
       <c r="C235" s="2">
-        <v>65.25</v>
+        <v>45.552131000000003</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E235" s="2">
         <v>-90</v>
@@ -5250,50 +5532,50 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="2" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="B236" s="2">
-        <v>55.65</v>
+        <v>40.97</v>
       </c>
       <c r="C236" s="2">
-        <v>61.85</v>
+        <v>28.95</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E236" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="2" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="B237" s="2">
-        <v>37.35</v>
+        <v>55.5</v>
       </c>
       <c r="C237" s="2">
-        <v>61.924999999999997</v>
+        <v>66.349999999999994</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E237" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="2" t="s">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="B238" s="2">
-        <v>35.85</v>
+        <v>54.4</v>
       </c>
       <c r="C238" s="2">
-        <v>61.924999999999997</v>
+        <v>63.2</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E238" s="2">
         <v>-90</v>
@@ -5301,50 +5583,50 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="2" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="B239" s="2">
-        <v>34.35</v>
+        <v>60.25</v>
       </c>
       <c r="C239" s="2">
-        <v>61.924999999999997</v>
+        <v>63.3</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E239" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="2" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="B240" s="2">
-        <v>2.7</v>
+        <v>54.3</v>
       </c>
       <c r="C240" s="2">
-        <v>58.825000000000003</v>
+        <v>65.790000000000006</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E240" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="2" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="B241" s="2">
-        <v>71.8</v>
+        <v>52.15</v>
       </c>
       <c r="C241" s="2">
-        <v>53</v>
+        <v>65.25</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E241" s="2">
         <v>-90</v>
@@ -5352,101 +5634,101 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="2" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="B242" s="2">
-        <v>54.45</v>
+        <v>6.34</v>
       </c>
       <c r="C242" s="2">
-        <v>61.3</v>
+        <v>44.1</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E242" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="2" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="B243" s="2">
-        <v>2.15</v>
+        <v>55.65</v>
       </c>
       <c r="C243" s="2">
-        <v>37.9</v>
+        <v>61.85</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E243" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="2" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="B244" s="2">
-        <v>2.15</v>
+        <v>47.78</v>
       </c>
       <c r="C244" s="2">
-        <v>42.1</v>
+        <v>20.3</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E244" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="2" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="B245" s="2">
-        <v>68.400000000000006</v>
+        <v>41.15</v>
       </c>
       <c r="C245" s="2">
-        <v>47.2</v>
+        <v>20.37</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E245" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="2" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="B246" s="2">
-        <v>12.3</v>
+        <v>39.15</v>
       </c>
       <c r="C246" s="2">
-        <v>49.3</v>
+        <v>19.8</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E246" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="2" t="s">
-        <v>214</v>
+        <v>319</v>
       </c>
       <c r="B247" s="2">
-        <v>2.65</v>
+        <v>31.788599000000001</v>
       </c>
       <c r="C247" s="2">
-        <v>25</v>
+        <v>50.693199999999997</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E247" s="2">
         <v>-90</v>
@@ -5454,220 +5736,220 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="2" t="s">
-        <v>215</v>
+        <v>320</v>
       </c>
       <c r="B248" s="2">
-        <v>2.15</v>
+        <v>28.51</v>
       </c>
       <c r="C248" s="2">
-        <v>35.799999999999997</v>
+        <v>23.09</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E248" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="2" t="s">
-        <v>216</v>
+        <v>321</v>
       </c>
       <c r="B249" s="2">
-        <v>2.15</v>
+        <v>28.52</v>
       </c>
       <c r="C249" s="2">
-        <v>40</v>
+        <v>24.6</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E249" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="2" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="B250" s="2">
-        <v>36.4</v>
+        <v>28.51</v>
       </c>
       <c r="C250" s="2">
-        <v>28.2</v>
+        <v>19.53</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E250" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="2" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="B251" s="2">
-        <v>38.799999999999997</v>
+        <v>28.53</v>
       </c>
       <c r="C251" s="2">
-        <v>28.2</v>
+        <v>21.09</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E251" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="2" t="s">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="B252" s="2">
-        <v>78</v>
+        <v>36.360599000000001</v>
       </c>
       <c r="C252" s="2">
-        <v>66.099999999999994</v>
+        <v>50.693199999999997</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E252" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="2" t="s">
-        <v>220</v>
+        <v>179</v>
       </c>
       <c r="B253" s="2">
-        <v>75.650000000000006</v>
+        <v>34.424999999999997</v>
       </c>
       <c r="C253" s="2">
-        <v>66.099999999999994</v>
+        <v>25.42</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E253" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="2" t="s">
-        <v>221</v>
+        <v>180</v>
       </c>
       <c r="B254" s="2">
-        <v>77.8</v>
+        <v>31.91</v>
       </c>
       <c r="C254" s="2">
-        <v>68.599999999999994</v>
+        <v>66.950468999999998</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E254" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="2" t="s">
-        <v>222</v>
+        <v>181</v>
       </c>
       <c r="B255" s="2">
-        <v>75.7</v>
+        <v>13.79</v>
       </c>
       <c r="C255" s="2">
-        <v>68.599999999999994</v>
+        <v>29.14</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E255" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="2" t="s">
-        <v>223</v>
+        <v>182</v>
       </c>
       <c r="B256" s="2">
-        <v>2.65</v>
+        <v>12.9</v>
       </c>
       <c r="C256" s="2">
-        <v>27.15</v>
+        <v>52.9</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E256" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="2" t="s">
-        <v>224</v>
+        <v>183</v>
       </c>
       <c r="B257" s="2">
-        <v>23.03</v>
+        <v>12.9</v>
       </c>
       <c r="C257" s="2">
-        <v>41.36</v>
+        <v>51.32</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E257" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="2" t="s">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="B258" s="2">
-        <v>20.8</v>
+        <v>52.65</v>
       </c>
       <c r="C258" s="2">
-        <v>41.2</v>
+        <v>56.35</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E258" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="2" t="s">
-        <v>226</v>
+        <v>185</v>
       </c>
       <c r="B259" s="2">
-        <v>6.75</v>
+        <v>51.1</v>
       </c>
       <c r="C259" s="2">
-        <v>61.1</v>
+        <v>56.35</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E259" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="2" t="s">
-        <v>227</v>
+        <v>186</v>
       </c>
       <c r="B260" s="2">
-        <v>27.75</v>
+        <v>60.2</v>
       </c>
       <c r="C260" s="2">
-        <v>61.15</v>
+        <v>60.3</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E260" s="2">
         <v>0</v>
@@ -5675,101 +5957,101 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="2" t="s">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="B261" s="2">
-        <v>56.8</v>
+        <v>37.35</v>
       </c>
       <c r="C261" s="2">
-        <v>38.429504999999999</v>
+        <v>61.924999999999997</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E261" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="2" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
       <c r="B262" s="2">
-        <v>13.4</v>
+        <v>35.85</v>
       </c>
       <c r="C262" s="2">
-        <v>45.1</v>
+        <v>61.924999999999997</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E262" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="2" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="B263" s="2">
-        <v>59.9</v>
+        <v>17.995207000000001</v>
       </c>
       <c r="C263" s="2">
-        <v>38.450000000000003</v>
+        <v>40.827131000000001</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E263" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="2" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="B264" s="2">
-        <v>22.74</v>
+        <v>17.996400000000001</v>
       </c>
       <c r="C264" s="2">
-        <v>67.459999999999994</v>
+        <v>39.827131000000001</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E264" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="2" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="B265" s="2">
-        <v>75.55</v>
+        <v>25.7</v>
       </c>
       <c r="C265" s="2">
-        <v>41.1</v>
+        <v>39</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E265" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="2" t="s">
-        <v>233</v>
+        <v>322</v>
       </c>
       <c r="B266" s="2">
-        <v>64.650000000000006</v>
+        <v>25.7</v>
       </c>
       <c r="C266" s="2">
-        <v>24.8</v>
+        <v>40.5</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E266" s="2">
         <v>0</v>
@@ -5777,33 +6059,33 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="2" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="B267" s="2">
-        <v>4.4000000000000004</v>
+        <v>20.5</v>
       </c>
       <c r="C267" s="2">
-        <v>17.5</v>
+        <v>37.049999999999997</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E267" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="2" t="s">
-        <v>235</v>
+        <v>323</v>
       </c>
       <c r="B268" s="2">
-        <v>59.35</v>
+        <v>22.44</v>
       </c>
       <c r="C268" s="2">
-        <v>24.75</v>
+        <v>38.6875</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E268" s="2">
         <v>0</v>
@@ -5811,16 +6093,16 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="2" t="s">
-        <v>236</v>
+        <v>192</v>
       </c>
       <c r="B269" s="2">
-        <v>52.65</v>
+        <v>28.7</v>
       </c>
       <c r="C269" s="2">
-        <v>59.91</v>
+        <v>30.95</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E269" s="2">
         <v>0</v>
@@ -5828,33 +6110,33 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="2" t="s">
-        <v>237</v>
+        <v>193</v>
       </c>
       <c r="B270" s="2">
-        <v>8.2891929999999991</v>
+        <v>28.7</v>
       </c>
       <c r="C270" s="2">
-        <v>49.317568999999999</v>
+        <v>32.5</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E270" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="2" t="s">
-        <v>238</v>
+        <v>194</v>
       </c>
       <c r="B271" s="2">
-        <v>11.900399999999999</v>
+        <v>69.23</v>
       </c>
       <c r="C271" s="2">
-        <v>36.243699999999997</v>
+        <v>15.5</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E271" s="2">
         <v>0</v>
@@ -5862,33 +6144,33 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="2" t="s">
-        <v>239</v>
+        <v>195</v>
       </c>
       <c r="B272" s="2">
-        <v>47.09</v>
+        <v>74.650000000000006</v>
       </c>
       <c r="C272" s="2">
-        <v>51.044800000000002</v>
+        <v>15.73</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E272" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="2" t="s">
-        <v>240</v>
+        <v>196</v>
       </c>
       <c r="B273" s="2">
-        <v>37.542892000000002</v>
+        <v>70.2</v>
       </c>
       <c r="C273" s="2">
-        <v>32.806668999999999</v>
+        <v>18.850000000000001</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E273" s="2">
         <v>90</v>
@@ -5896,118 +6178,118 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="2" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="B274" s="2">
-        <v>45.543892</v>
+        <v>71.7</v>
       </c>
       <c r="C274" s="2">
-        <v>32.743169000000002</v>
+        <v>18.850000000000001</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E274" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="2" t="s">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="B275" s="2">
-        <v>26.31</v>
+        <v>74.55</v>
       </c>
       <c r="C275" s="2">
-        <v>65.83</v>
+        <v>21</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E275" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="2" t="s">
-        <v>243</v>
+        <v>199</v>
       </c>
       <c r="B276" s="2">
-        <v>46.174999999999997</v>
+        <v>71.069999999999993</v>
       </c>
       <c r="C276" s="2">
-        <v>13.4</v>
+        <v>21</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E276" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="2" t="s">
-        <v>244</v>
+        <v>200</v>
       </c>
       <c r="B277" s="2">
-        <v>34.9</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="C277" s="2">
-        <v>13.1</v>
+        <v>18.649999999999999</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E277" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="2" t="s">
-        <v>288</v>
+        <v>201</v>
       </c>
       <c r="B278" s="2">
-        <v>68.72</v>
+        <v>75.62</v>
       </c>
       <c r="C278" s="2">
-        <v>38.74</v>
+        <v>15.72</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E278" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="2" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="B279" s="2">
-        <v>73.59</v>
+        <v>74.650000000000006</v>
       </c>
       <c r="C279" s="2">
-        <v>44.697499999999998</v>
+        <v>9.6</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E279" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="2" t="s">
-        <v>245</v>
+        <v>325</v>
       </c>
       <c r="B280" s="2">
-        <v>19.774799999999999</v>
+        <v>23.934999999999999</v>
       </c>
       <c r="C280" s="2">
-        <v>47.496400000000001</v>
+        <v>29.4</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E280" s="2">
         <v>0</v>
@@ -6015,16 +6297,16 @@
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="2" t="s">
-        <v>246</v>
+        <v>326</v>
       </c>
       <c r="B281" s="2">
-        <v>34.430199000000002</v>
+        <v>23.934999999999999</v>
       </c>
       <c r="C281" s="2">
-        <v>45.816400000000002</v>
+        <v>27.85</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E281" s="2">
         <v>0</v>
@@ -6032,33 +6314,33 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="2" t="s">
-        <v>247</v>
+        <v>327</v>
       </c>
       <c r="B282" s="2">
-        <v>55.611891999999997</v>
+        <v>71.8</v>
       </c>
       <c r="C282" s="2">
-        <v>46.441169000000002</v>
+        <v>53</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E282" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="2" t="s">
-        <v>248</v>
+        <v>328</v>
       </c>
       <c r="B283" s="2">
-        <v>65.75</v>
+        <v>76.8</v>
       </c>
       <c r="C283" s="2">
-        <v>47.15</v>
+        <v>57.75</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E283" s="2">
         <v>90</v>
@@ -6066,55 +6348,1618 @@
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="2" t="s">
-        <v>249</v>
+        <v>329</v>
       </c>
       <c r="B284" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="C284" s="2">
+        <v>58.825000000000003</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E284" s="2">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B285" s="2">
+        <v>54.45</v>
+      </c>
+      <c r="C285" s="2">
+        <v>61.3</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E285" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B286" s="2">
+        <v>22.74</v>
+      </c>
+      <c r="C286" s="2">
+        <v>67.459999999999994</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E286" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B287" s="2">
+        <v>75.55</v>
+      </c>
+      <c r="C287" s="2">
+        <v>41.1</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E287" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B288" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="C288" s="2">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E288" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B289" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="C289" s="2">
+        <v>37.9</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E289" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B290" s="2">
+        <v>78</v>
+      </c>
+      <c r="C290" s="2">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E290" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B291" s="2">
+        <v>75.650000000000006</v>
+      </c>
+      <c r="C291" s="2">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E291" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B292" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="C292" s="2">
+        <v>42.1</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E292" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B293" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="C293" s="2">
+        <v>40</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E293" s="2">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B294" s="2">
+        <v>56.8</v>
+      </c>
+      <c r="C294" s="2">
+        <v>38.429504999999999</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E294" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B295" s="2">
+        <v>75.349999999999994</v>
+      </c>
+      <c r="C295" s="2">
+        <v>27.1</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E295" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B296" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C296" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E296" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B297" s="2">
+        <v>75.3</v>
+      </c>
+      <c r="C297" s="2">
+        <v>31.9</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E297" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B298" s="2">
+        <v>59.9</v>
+      </c>
+      <c r="C298" s="2">
+        <v>38.450000000000003</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E298" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B299" s="2">
+        <v>37.89</v>
+      </c>
+      <c r="C299" s="2">
+        <v>12.12</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E299" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B300" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="C300" s="2">
+        <v>12.2</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E300" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B301" s="2">
+        <v>33.049999999999997</v>
+      </c>
+      <c r="C301" s="2">
+        <v>10.25</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E301" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B302" s="2">
+        <v>40.549999999999997</v>
+      </c>
+      <c r="C302" s="2">
+        <v>2.35</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E302" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B303" s="2">
+        <v>33.049999999999997</v>
+      </c>
+      <c r="C303" s="2">
+        <v>8.25</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E303" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B304" s="2">
+        <v>78</v>
+      </c>
+      <c r="C304" s="2">
+        <v>63.85</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E304" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B305" s="2">
+        <v>75.650000000000006</v>
+      </c>
+      <c r="C305" s="2">
+        <v>63.85</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E305" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B306" s="2">
+        <v>58.9</v>
+      </c>
+      <c r="C306" s="2">
+        <v>11.9</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E306" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B307" s="2">
+        <v>22.13</v>
+      </c>
+      <c r="C307" s="2">
+        <v>3.02</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E307" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B308" s="2">
+        <v>77.8</v>
+      </c>
+      <c r="C308" s="2">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E308" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B309" s="2">
+        <v>75.7</v>
+      </c>
+      <c r="C309" s="2">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E309" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B310" s="2">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="C310" s="2">
+        <v>47.2</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E310" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B311" s="2">
+        <v>6.75</v>
+      </c>
+      <c r="C311" s="2">
+        <v>61.1</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E311" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B312" s="2">
+        <v>36.4</v>
+      </c>
+      <c r="C312" s="2">
+        <v>28.2</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E312" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B313" s="2">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="C313" s="2">
+        <v>28.2</v>
+      </c>
+      <c r="D313" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E313" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B314" s="2">
+        <v>27.75</v>
+      </c>
+      <c r="C314" s="2">
+        <v>61.15</v>
+      </c>
+      <c r="D314" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E314" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B315" s="2">
+        <v>2.65</v>
+      </c>
+      <c r="C315" s="2">
+        <v>25</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E315" s="2">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B316" s="2">
+        <v>2.65</v>
+      </c>
+      <c r="C316" s="2">
+        <v>27.15</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E316" s="2">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B317" s="2">
+        <v>23.03</v>
+      </c>
+      <c r="C317" s="2">
+        <v>41.36</v>
+      </c>
+      <c r="D317" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E317" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B318" s="2">
+        <v>20.8</v>
+      </c>
+      <c r="C318" s="2">
+        <v>41.2</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E318" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B319" s="2">
+        <v>12.3</v>
+      </c>
+      <c r="C319" s="2">
+        <v>49.3</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E319" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B320" s="2">
+        <v>13.4</v>
+      </c>
+      <c r="C320" s="2">
+        <v>45.1</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E320" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B321" s="2">
+        <v>26.31</v>
+      </c>
+      <c r="C321" s="2">
+        <v>65.83</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E321" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B322" s="2">
+        <v>68.72</v>
+      </c>
+      <c r="C322" s="2">
+        <v>38.74</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E322" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B323" s="2">
+        <v>73.59</v>
+      </c>
+      <c r="C323" s="2">
+        <v>44.697499999999998</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E323" s="2">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B324" s="2">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="C324" s="2">
+        <v>4.45</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E324" s="2">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B325" s="2">
+        <v>41.65</v>
+      </c>
+      <c r="C325" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E325" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B326" s="2">
+        <v>36.549999999999997</v>
+      </c>
+      <c r="C326" s="2">
+        <v>5.15</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E326" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B327" s="2">
+        <v>42.68</v>
+      </c>
+      <c r="C327" s="2">
+        <v>6.43</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E327" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B328" s="2">
+        <v>38.43</v>
+      </c>
+      <c r="C328" s="2">
+        <v>10.975</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E328" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B329" s="2">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="C329" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E329" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B330" s="2">
+        <v>41.71</v>
+      </c>
+      <c r="C330" s="2">
+        <v>10.975</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E330" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B331" s="2">
+        <v>53.15</v>
+      </c>
+      <c r="C331" s="2">
+        <v>8.08</v>
+      </c>
+      <c r="D331" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E331" s="2">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B332" s="2">
+        <v>29.180800000000001</v>
+      </c>
+      <c r="C332" s="2">
+        <v>5.7000010000000003</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E332" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B333" s="2">
+        <v>25.25</v>
+      </c>
+      <c r="C333" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E333" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B334" s="2">
+        <v>47.09</v>
+      </c>
+      <c r="C334" s="2">
+        <v>51.044800000000002</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E334" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B335" s="2">
+        <v>65.75</v>
+      </c>
+      <c r="C335" s="2">
+        <v>47.15</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E335" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B336" s="2">
+        <v>55.611891999999997</v>
+      </c>
+      <c r="C336" s="2">
+        <v>46.441169000000002</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E336" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B337" s="2">
+        <v>37.542892000000002</v>
+      </c>
+      <c r="C337" s="2">
+        <v>32.806668999999999</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E337" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B338" s="2">
+        <v>19.774799999999999</v>
+      </c>
+      <c r="C338" s="2">
+        <v>47.496400000000001</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E338" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B339" s="2">
+        <v>45.543892</v>
+      </c>
+      <c r="C339" s="2">
+        <v>32.743169000000002</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E339" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B340" s="2">
+        <v>8.2891929999999991</v>
+      </c>
+      <c r="C340" s="2">
+        <v>49.317568999999999</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E340" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B341" s="2">
+        <v>45.1</v>
+      </c>
+      <c r="C341" s="2">
+        <v>22.55</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E341" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B342" s="2">
+        <v>34.85</v>
+      </c>
+      <c r="C342" s="2">
+        <v>22.65</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E342" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B343" s="2">
+        <v>52.65</v>
+      </c>
+      <c r="C343" s="2">
+        <v>59.91</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E343" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B344" s="2">
+        <v>34.430199000000002</v>
+      </c>
+      <c r="C344" s="2">
+        <v>45.816400000000002</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E344" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B345" s="2">
+        <v>11.900399999999999</v>
+      </c>
+      <c r="C345" s="2">
+        <v>36.243699999999997</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E345" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B346" s="2">
+        <v>26.1</v>
+      </c>
+      <c r="C346" s="2">
+        <v>35.85</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E346" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B347" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="C347" s="2">
+        <v>36.049999999999997</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E347" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B348" s="2">
+        <v>74.5</v>
+      </c>
+      <c r="C348" s="2">
+        <v>23.35</v>
+      </c>
+      <c r="D348" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E348" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B349" s="2">
+        <v>71.3</v>
+      </c>
+      <c r="C349" s="2">
+        <v>24.3</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E349" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B350" s="2">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="C350" s="2">
+        <v>12.7</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E350" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B351" s="2">
         <v>11.82</v>
       </c>
-      <c r="C284" s="2">
+      <c r="C351" s="2">
         <v>29.12</v>
       </c>
-      <c r="D284" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E284" s="2">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5">
-      <c r="A285" s="2"/>
-      <c r="B285" s="2"/>
-      <c r="C285" s="2"/>
-      <c r="D285" s="2"/>
-      <c r="E285" s="2"/>
-    </row>
-    <row r="286" spans="1:5">
-      <c r="A286" s="2"/>
-      <c r="B286" s="2"/>
-      <c r="C286" s="2"/>
-      <c r="D286" s="2"/>
-      <c r="E286" s="2"/>
-    </row>
-    <row r="287" spans="1:5">
-      <c r="A287" s="2"/>
-      <c r="B287" s="2"/>
-      <c r="C287" s="2"/>
-      <c r="D287" s="2"/>
-      <c r="E287" s="2"/>
-    </row>
-    <row r="288" spans="1:5">
-      <c r="A288" s="2"/>
-      <c r="B288" s="2"/>
-      <c r="C288" s="2"/>
-      <c r="D288" s="2"/>
-      <c r="E288" s="2"/>
-    </row>
-    <row r="289" spans="1:5">
-      <c r="A289" s="2"/>
-      <c r="B289" s="2"/>
-      <c r="C289" s="2"/>
-      <c r="D289" s="2"/>
-      <c r="E289" s="2"/>
+      <c r="D351" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E351" s="2">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B352" s="2">
+        <v>41.65</v>
+      </c>
+      <c r="C352" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E352" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B353" s="2">
+        <v>36.549999999999997</v>
+      </c>
+      <c r="C353" s="2">
+        <v>5.15</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E353" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B354" s="2">
+        <v>42.68</v>
+      </c>
+      <c r="C354" s="2">
+        <v>6.43</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E354" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B355" s="2">
+        <v>38.43</v>
+      </c>
+      <c r="C355" s="2">
+        <v>10.975</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E355" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B356" s="2">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="C356" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E356" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B357" s="2">
+        <v>41.71</v>
+      </c>
+      <c r="C357" s="2">
+        <v>10.975</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E357" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B358" s="2">
+        <v>53.15</v>
+      </c>
+      <c r="C358" s="2">
+        <v>8.08</v>
+      </c>
+      <c r="D358" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E358" s="2">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B359" s="2">
+        <v>29.180800000000001</v>
+      </c>
+      <c r="C359" s="2">
+        <v>5.7000010000000003</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E359" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B360" s="2">
+        <v>25.25</v>
+      </c>
+      <c r="C360" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="D360" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E360" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B361" s="2">
+        <v>47.09</v>
+      </c>
+      <c r="C361" s="2">
+        <v>51.044800000000002</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E361" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B362" s="2">
+        <v>65.75</v>
+      </c>
+      <c r="C362" s="2">
+        <v>47.15</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E362" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B363" s="2">
+        <v>55.611891999999997</v>
+      </c>
+      <c r="C363" s="2">
+        <v>46.441169000000002</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E363" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B364" s="2">
+        <v>37.542892000000002</v>
+      </c>
+      <c r="C364" s="2">
+        <v>32.806668999999999</v>
+      </c>
+      <c r="D364" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E364" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B365" s="2">
+        <v>19.774799999999999</v>
+      </c>
+      <c r="C365" s="2">
+        <v>47.496400000000001</v>
+      </c>
+      <c r="D365" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E365" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B366" s="2">
+        <v>45.543892</v>
+      </c>
+      <c r="C366" s="2">
+        <v>32.743169000000002</v>
+      </c>
+      <c r="D366" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E366" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B367" s="2">
+        <v>8.2891929999999991</v>
+      </c>
+      <c r="C367" s="2">
+        <v>49.317568999999999</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E367" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B368" s="2">
+        <v>45.1</v>
+      </c>
+      <c r="C368" s="2">
+        <v>22.55</v>
+      </c>
+      <c r="D368" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E368" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B369" s="2">
+        <v>34.85</v>
+      </c>
+      <c r="C369" s="2">
+        <v>22.65</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E369" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B370" s="2">
+        <v>52.65</v>
+      </c>
+      <c r="C370" s="2">
+        <v>59.91</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E370" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B371" s="2">
+        <v>34.430199000000002</v>
+      </c>
+      <c r="C371" s="2">
+        <v>45.816400000000002</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E371" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B372" s="2">
+        <v>11.900399999999999</v>
+      </c>
+      <c r="C372" s="2">
+        <v>36.243699999999997</v>
+      </c>
+      <c r="D372" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E372" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B373" s="2">
+        <v>26.1</v>
+      </c>
+      <c r="C373" s="2">
+        <v>35.85</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E373" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B374" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="C374" s="2">
+        <v>36.049999999999997</v>
+      </c>
+      <c r="D374" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E374" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B375" s="2">
+        <v>74.5</v>
+      </c>
+      <c r="C375" s="2">
+        <v>23.35</v>
+      </c>
+      <c r="D375" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E375" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B376" s="2">
+        <v>71.3</v>
+      </c>
+      <c r="C376" s="2">
+        <v>24.3</v>
+      </c>
+      <c r="D376" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E376" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B377" s="2">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="C377" s="2">
+        <v>12.7</v>
+      </c>
+      <c r="D377" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E377" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B378" s="2">
+        <v>11.82</v>
+      </c>
+      <c r="C378" s="2">
+        <v>29.12</v>
+      </c>
+      <c r="D378" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E378" s="2">
+        <v>-90</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
